--- a/research/traditional_assets/database/data/vietnam/vietnam_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_retail_automotive.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1051296235157854</v>
+        <v>0.1049553642687538</v>
       </c>
       <c r="C2">
-        <v>16.05798260211745</v>
+        <v>15.92408310575387</v>
       </c>
       <c r="D2">
-        <v>14.65798260211745</v>
+        <v>14.68268310575387</v>
       </c>
       <c r="E2">
-        <v>-2.16</v>
+        <v>-2.0014</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1586</v>
       </c>
       <c r="G2">
         <v>1.4</v>
@@ -1582,28 +1582,28 @@
         <v>2.02</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00797758</v>
       </c>
       <c r="N2">
-        <v>2.02</v>
+        <v>2.01202242</v>
       </c>
       <c r="O2">
-        <v>0.404</v>
+        <v>0.4024044840000001</v>
       </c>
       <c r="P2">
-        <v>1.616</v>
+        <v>1.609617936</v>
       </c>
       <c r="Q2">
-        <v>1.786</v>
+        <v>1.779617936</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1051296235157854</v>
+        <v>0.105609054816923</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7164970653807063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>253.2096199599378</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1049553642687538</v>
+        <v>0.1047811050217222</v>
       </c>
       <c r="C3">
-        <v>15.92408310575387</v>
+        <v>15.79026699668178</v>
       </c>
       <c r="D3">
-        <v>14.68268310575387</v>
+        <v>14.70746699668178</v>
       </c>
       <c r="E3">
-        <v>-2.0014</v>
+        <v>-1.8428</v>
       </c>
       <c r="F3">
-        <v>0.1586</v>
+        <v>0.3172</v>
       </c>
       <c r="G3">
         <v>1.4</v>
@@ -1664,28 +1664,28 @@
         <v>2.02</v>
       </c>
       <c r="M3">
-        <v>0.00797758</v>
+        <v>0.01595516</v>
       </c>
       <c r="N3">
-        <v>2.01202242</v>
+        <v>2.00404484</v>
       </c>
       <c r="O3">
-        <v>0.4024044840000001</v>
+        <v>0.400808968</v>
       </c>
       <c r="P3">
-        <v>1.609617936</v>
+        <v>1.603235872</v>
       </c>
       <c r="Q3">
-        <v>1.779617936</v>
+        <v>1.773235872</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.105609054816923</v>
+        <v>0.1060982704303288</v>
       </c>
       <c r="T3">
-        <v>0.7164970653807063</v>
+        <v>0.7223577423704466</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>253.2096199599378</v>
+        <v>126.6048099799689</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1047811050217222</v>
+        <v>0.1046068457746907</v>
       </c>
       <c r="C4">
-        <v>15.79026699668178</v>
+        <v>15.65653469788025</v>
       </c>
       <c r="D4">
-        <v>14.70746699668178</v>
+        <v>14.73233469788025</v>
       </c>
       <c r="E4">
-        <v>-1.8428</v>
+        <v>-1.6842</v>
       </c>
       <c r="F4">
-        <v>0.3172</v>
+        <v>0.4757999999999999</v>
       </c>
       <c r="G4">
         <v>1.4</v>
@@ -1746,28 +1746,28 @@
         <v>2.02</v>
       </c>
       <c r="M4">
-        <v>0.01595516</v>
+        <v>0.02393274</v>
       </c>
       <c r="N4">
-        <v>2.00404484</v>
+        <v>1.99606726</v>
       </c>
       <c r="O4">
-        <v>0.400808968</v>
+        <v>0.399213452</v>
       </c>
       <c r="P4">
-        <v>1.603235872</v>
+        <v>1.596853808</v>
       </c>
       <c r="Q4">
-        <v>1.773235872</v>
+        <v>1.766853808</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1060982704303288</v>
+        <v>0.1065975729635986</v>
       </c>
       <c r="T4">
-        <v>0.7223577423704466</v>
+        <v>0.7283392580610063</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>126.6048099799689</v>
+        <v>84.40320665331258</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1046068457746907</v>
+        <v>0.1044325865276591</v>
       </c>
       <c r="C5">
-        <v>15.65653469788025</v>
+        <v>15.52288663519393</v>
       </c>
       <c r="D5">
-        <v>14.73233469788025</v>
+        <v>14.75728663519393</v>
       </c>
       <c r="E5">
-        <v>-1.6842</v>
+        <v>-1.5256</v>
       </c>
       <c r="F5">
-        <v>0.4757999999999999</v>
+        <v>0.6344</v>
       </c>
       <c r="G5">
         <v>1.4</v>
@@ -1828,28 +1828,28 @@
         <v>2.02</v>
       </c>
       <c r="M5">
-        <v>0.02393274</v>
+        <v>0.03191032</v>
       </c>
       <c r="N5">
-        <v>1.99606726</v>
+        <v>1.98808968</v>
       </c>
       <c r="O5">
-        <v>0.399213452</v>
+        <v>0.3976179360000001</v>
       </c>
       <c r="P5">
-        <v>1.596853808</v>
+        <v>1.590471744</v>
       </c>
       <c r="Q5">
-        <v>1.766853808</v>
+        <v>1.760471744</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1065975729635986</v>
+        <v>0.1071072776329782</v>
       </c>
       <c r="T5">
-        <v>0.7283392580610063</v>
+        <v>0.7344453886617862</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.40320665331258</v>
+        <v>63.30240498998444</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1044325865276591</v>
+        <v>0.1042583272806275</v>
       </c>
       <c r="C6">
-        <v>15.52288663519393</v>
+        <v>15.38932323735735</v>
       </c>
       <c r="D6">
-        <v>14.75728663519393</v>
+        <v>14.78232323735735</v>
       </c>
       <c r="E6">
-        <v>-1.5256</v>
+        <v>-1.367</v>
       </c>
       <c r="F6">
-        <v>0.6344</v>
+        <v>0.793</v>
       </c>
       <c r="G6">
         <v>1.4</v>
@@ -1910,28 +1910,28 @@
         <v>2.02</v>
       </c>
       <c r="M6">
-        <v>0.03191032</v>
+        <v>0.0398879</v>
       </c>
       <c r="N6">
-        <v>1.98808968</v>
+        <v>1.9801121</v>
       </c>
       <c r="O6">
-        <v>0.3976179360000001</v>
+        <v>0.39602242</v>
       </c>
       <c r="P6">
-        <v>1.590471744</v>
+        <v>1.58408968</v>
       </c>
       <c r="Q6">
-        <v>1.760471744</v>
+        <v>1.75408968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1071072776329782</v>
+        <v>0.1076277129269763</v>
       </c>
       <c r="T6">
-        <v>0.7344453886617862</v>
+        <v>0.7406800693804769</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.30240498998444</v>
+        <v>50.64192399198755</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1042583272806275</v>
+        <v>0.1040840680335959</v>
       </c>
       <c r="C7">
-        <v>15.38932323735735</v>
+        <v>15.25584493601946</v>
       </c>
       <c r="D7">
-        <v>14.78232323735735</v>
+        <v>14.80744493601946</v>
       </c>
       <c r="E7">
-        <v>-1.367</v>
+        <v>-1.2084</v>
       </c>
       <c r="F7">
-        <v>0.793</v>
+        <v>0.9516</v>
       </c>
       <c r="G7">
         <v>1.4</v>
@@ -1992,28 +1992,28 @@
         <v>2.02</v>
       </c>
       <c r="M7">
-        <v>0.0398879</v>
+        <v>0.04786547999999999</v>
       </c>
       <c r="N7">
-        <v>1.9801121</v>
+        <v>1.97213452</v>
       </c>
       <c r="O7">
-        <v>0.39602242</v>
+        <v>0.394426904</v>
       </c>
       <c r="P7">
-        <v>1.58408968</v>
+        <v>1.577707616</v>
       </c>
       <c r="Q7">
-        <v>1.75408968</v>
+        <v>1.747707616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1076277129269763</v>
+        <v>0.1081592213123361</v>
       </c>
       <c r="T7">
-        <v>0.7406800693804769</v>
+        <v>0.7470474028804167</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.64192399198755</v>
+        <v>42.20160332665629</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1040840680335959</v>
+        <v>0.1039098087865644</v>
       </c>
       <c r="C8">
-        <v>15.25584493601946</v>
+        <v>15.12245216576848</v>
       </c>
       <c r="D8">
-        <v>14.80744493601946</v>
+        <v>14.83265216576848</v>
       </c>
       <c r="E8">
-        <v>-1.2084</v>
+        <v>-1.0498</v>
       </c>
       <c r="F8">
-        <v>0.9515999999999999</v>
+        <v>1.1102</v>
       </c>
       <c r="G8">
         <v>1.4</v>
@@ -2074,28 +2074,28 @@
         <v>2.02</v>
       </c>
       <c r="M8">
-        <v>0.04786547999999999</v>
+        <v>0.05584305999999999</v>
       </c>
       <c r="N8">
-        <v>1.97213452</v>
+        <v>1.96415694</v>
       </c>
       <c r="O8">
-        <v>0.394426904</v>
+        <v>0.3928313880000001</v>
       </c>
       <c r="P8">
-        <v>1.577707616</v>
+        <v>1.571325552</v>
       </c>
       <c r="Q8">
-        <v>1.747707616</v>
+        <v>1.741325552</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1081592213123361</v>
+        <v>0.1087021599855531</v>
       </c>
       <c r="T8">
-        <v>0.7470474028804167</v>
+        <v>0.7535516682835808</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.20160332665629</v>
+        <v>36.17280285141968</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1039098087865644</v>
+        <v>0.1037355495395328</v>
       </c>
       <c r="C9">
-        <v>15.12245216576848</v>
+        <v>14.98914536415692</v>
       </c>
       <c r="D9">
-        <v>14.83265216576848</v>
+        <v>14.85794536415692</v>
       </c>
       <c r="E9">
-        <v>-1.0498</v>
+        <v>-0.8912000000000002</v>
       </c>
       <c r="F9">
-        <v>1.1102</v>
+        <v>1.2688</v>
       </c>
       <c r="G9">
         <v>1.4</v>
@@ -2156,28 +2156,28 @@
         <v>2.02</v>
       </c>
       <c r="M9">
-        <v>0.05584306</v>
+        <v>0.06382064</v>
       </c>
       <c r="N9">
-        <v>1.96415694</v>
+        <v>1.95617936</v>
       </c>
       <c r="O9">
-        <v>0.3928313880000001</v>
+        <v>0.391235872</v>
       </c>
       <c r="P9">
-        <v>1.571325552</v>
+        <v>1.564943488</v>
       </c>
       <c r="Q9">
-        <v>1.741325552</v>
+        <v>1.734943488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1087021599855531</v>
+        <v>0.1092569016734052</v>
       </c>
       <c r="T9">
-        <v>0.7535516682835808</v>
+        <v>0.7601973307607267</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.17280285141968</v>
+        <v>31.65120249499222</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1037355495395328</v>
+        <v>0.1035612902925012</v>
       </c>
       <c r="C10">
-        <v>14.98914536415692</v>
+        <v>14.85592497172693</v>
       </c>
       <c r="D10">
-        <v>14.85794536415692</v>
+        <v>14.88332497172693</v>
       </c>
       <c r="E10">
-        <v>-0.8912000000000002</v>
+        <v>-0.7326000000000001</v>
       </c>
       <c r="F10">
-        <v>1.2688</v>
+        <v>1.4274</v>
       </c>
       <c r="G10">
         <v>1.4</v>
@@ -2238,28 +2238,28 @@
         <v>2.02</v>
       </c>
       <c r="M10">
-        <v>0.06382064</v>
+        <v>0.07179822</v>
       </c>
       <c r="N10">
-        <v>1.95617936</v>
+        <v>1.94820178</v>
       </c>
       <c r="O10">
-        <v>0.391235872</v>
+        <v>0.389640356</v>
       </c>
       <c r="P10">
-        <v>1.564943488</v>
+        <v>1.558561424</v>
       </c>
       <c r="Q10">
-        <v>1.734943488</v>
+        <v>1.728561424</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1092569016734052</v>
+        <v>0.1098238354862651</v>
       </c>
       <c r="T10">
-        <v>0.7601973307607267</v>
+        <v>0.7669890517538539</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.65120249499222</v>
+        <v>28.13440221777086</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1035612902925012</v>
+        <v>0.1033870310454697</v>
       </c>
       <c r="C11">
-        <v>14.85592497172693</v>
+        <v>14.72279143203583</v>
       </c>
       <c r="D11">
-        <v>14.88332497172693</v>
+        <v>14.90879143203583</v>
       </c>
       <c r="E11">
-        <v>-0.7326000000000001</v>
+        <v>-0.5740000000000003</v>
       </c>
       <c r="F11">
-        <v>1.4274</v>
+        <v>1.586</v>
       </c>
       <c r="G11">
         <v>1.4</v>
@@ -2320,28 +2320,28 @@
         <v>2.02</v>
       </c>
       <c r="M11">
-        <v>0.07179822</v>
+        <v>0.07977579999999999</v>
       </c>
       <c r="N11">
-        <v>1.94820178</v>
+        <v>1.9402242</v>
       </c>
       <c r="O11">
-        <v>0.389640356</v>
+        <v>0.3880448400000001</v>
       </c>
       <c r="P11">
-        <v>1.558561424</v>
+        <v>1.55217936</v>
       </c>
       <c r="Q11">
-        <v>1.728561424</v>
+        <v>1.72217936</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1098238354862651</v>
+        <v>0.1104033678282996</v>
       </c>
       <c r="T11">
-        <v>0.7669890517538539</v>
+        <v>0.7739316998801616</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.13440221777086</v>
+        <v>25.32096199599378</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1033870310454697</v>
+        <v>0.1032127717984381</v>
       </c>
       <c r="C12">
-        <v>14.72279143203582</v>
+        <v>14.589745191682</v>
       </c>
       <c r="D12">
-        <v>14.90879143203583</v>
+        <v>14.934345191682</v>
       </c>
       <c r="E12">
-        <v>-0.5740000000000001</v>
+        <v>-0.4154000000000002</v>
       </c>
       <c r="F12">
-        <v>1.586</v>
+        <v>1.7446</v>
       </c>
       <c r="G12">
         <v>1.4</v>
@@ -2402,28 +2402,28 @@
         <v>2.02</v>
       </c>
       <c r="M12">
-        <v>0.07977579999999999</v>
+        <v>0.08775337999999999</v>
       </c>
       <c r="N12">
-        <v>1.9402242</v>
+        <v>1.93224662</v>
       </c>
       <c r="O12">
-        <v>0.3880448400000001</v>
+        <v>0.386449324</v>
       </c>
       <c r="P12">
-        <v>1.55217936</v>
+        <v>1.545797296</v>
       </c>
       <c r="Q12">
-        <v>1.72217936</v>
+        <v>1.715797296</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1104033678282997</v>
+        <v>0.1109959233690316</v>
       </c>
       <c r="T12">
-        <v>0.7739316998801619</v>
+        <v>0.7810303625711056</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.32096199599378</v>
+        <v>23.01905635999434</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1032127717984381</v>
+        <v>0.1030385125514065</v>
       </c>
       <c r="C13">
-        <v>14.589745191682</v>
+        <v>14.45678670033097</v>
       </c>
       <c r="D13">
-        <v>14.934345191682</v>
+        <v>14.95998670033097</v>
       </c>
       <c r="E13">
-        <v>-0.4154000000000002</v>
+        <v>-0.2568000000000004</v>
       </c>
       <c r="F13">
-        <v>1.7446</v>
+        <v>1.9032</v>
       </c>
       <c r="G13">
         <v>1.4</v>
@@ -2484,28 +2484,28 @@
         <v>2.02</v>
       </c>
       <c r="M13">
-        <v>0.08775337999999999</v>
+        <v>0.09573095999999999</v>
       </c>
       <c r="N13">
-        <v>1.93224662</v>
+        <v>1.92426904</v>
       </c>
       <c r="O13">
-        <v>0.386449324</v>
+        <v>0.384853808</v>
       </c>
       <c r="P13">
-        <v>1.545797296</v>
+        <v>1.539415232</v>
       </c>
       <c r="Q13">
-        <v>1.715797296</v>
+        <v>1.709415232</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1109959233690316</v>
+        <v>0.1116019460811438</v>
       </c>
       <c r="T13">
-        <v>0.7810303625711056</v>
+        <v>0.7882903585050256</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.01905635999434</v>
+        <v>21.10080166332814</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1030385125514065</v>
+        <v>0.102864253304375</v>
       </c>
       <c r="C14">
-        <v>14.45678670033097</v>
+        <v>14.32391641074178</v>
       </c>
       <c r="D14">
-        <v>14.95998670033097</v>
+        <v>14.98571641074178</v>
       </c>
       <c r="E14">
-        <v>-0.2568000000000004</v>
+        <v>-0.09820000000000029</v>
       </c>
       <c r="F14">
-        <v>1.9032</v>
+        <v>2.0618</v>
       </c>
       <c r="G14">
         <v>1.4</v>
@@ -2566,28 +2566,28 @@
         <v>2.02</v>
       </c>
       <c r="M14">
-        <v>0.09573095999999999</v>
+        <v>0.10370854</v>
       </c>
       <c r="N14">
-        <v>1.92426904</v>
+        <v>1.91629146</v>
       </c>
       <c r="O14">
-        <v>0.384853808</v>
+        <v>0.3832582920000001</v>
       </c>
       <c r="P14">
-        <v>1.539415232</v>
+        <v>1.533033168</v>
       </c>
       <c r="Q14">
-        <v>1.709415232</v>
+        <v>1.703033168</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1116019460811438</v>
+        <v>0.1122219003498563</v>
       </c>
       <c r="T14">
-        <v>0.7882903585050256</v>
+        <v>0.7957172508971965</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.10080166332814</v>
+        <v>19.47766307384137</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.102864253304375</v>
+        <v>0.1026899940573434</v>
       </c>
       <c r="C15">
-        <v>14.32391641074178</v>
+        <v>14.19113477879364</v>
       </c>
       <c r="D15">
-        <v>14.98571641074178</v>
+        <v>15.01153477879364</v>
       </c>
       <c r="E15">
-        <v>-0.09820000000000029</v>
+        <v>0.06040000000000001</v>
       </c>
       <c r="F15">
-        <v>2.0618</v>
+        <v>2.2204</v>
       </c>
       <c r="G15">
         <v>1.4</v>
@@ -2648,28 +2648,28 @@
         <v>2.02</v>
       </c>
       <c r="M15">
-        <v>0.10370854</v>
+        <v>0.11168612</v>
       </c>
       <c r="N15">
-        <v>1.91629146</v>
+        <v>1.90831388</v>
       </c>
       <c r="O15">
-        <v>0.3832582920000001</v>
+        <v>0.381662776</v>
       </c>
       <c r="P15">
-        <v>1.533033168</v>
+        <v>1.526651104</v>
       </c>
       <c r="Q15">
-        <v>1.703033168</v>
+        <v>1.696651104</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1122219003498563</v>
+        <v>0.1128562721597016</v>
       </c>
       <c r="T15">
-        <v>0.7957172508971965</v>
+        <v>0.8033168617170924</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.47766307384137</v>
+        <v>18.08640142570984</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1026899940573434</v>
+        <v>0.1025157348103118</v>
       </c>
       <c r="C16">
-        <v>14.19113477879364</v>
+        <v>14.05844226351287</v>
       </c>
       <c r="D16">
-        <v>15.01153477879364</v>
+        <v>15.03744226351288</v>
       </c>
       <c r="E16">
-        <v>0.06040000000000001</v>
+        <v>0.2190000000000003</v>
       </c>
       <c r="F16">
-        <v>2.2204</v>
+        <v>2.379</v>
       </c>
       <c r="G16">
         <v>1.4</v>
@@ -2730,28 +2730,28 @@
         <v>2.02</v>
       </c>
       <c r="M16">
-        <v>0.11168612</v>
+        <v>0.1196637</v>
       </c>
       <c r="N16">
-        <v>1.90831388</v>
+        <v>1.9003363</v>
       </c>
       <c r="O16">
-        <v>0.381662776</v>
+        <v>0.38006726</v>
       </c>
       <c r="P16">
-        <v>1.526651104</v>
+        <v>1.52026904</v>
       </c>
       <c r="Q16">
-        <v>1.696651104</v>
+        <v>1.69026904</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1128562721597016</v>
+        <v>0.1135055703650727</v>
       </c>
       <c r="T16">
-        <v>0.8033168617170924</v>
+        <v>0.8110952869092211</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.08640142570984</v>
+        <v>16.88064133066251</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1025157348103118</v>
+        <v>0.1023414755632802</v>
       </c>
       <c r="C17">
-        <v>14.05844226351287</v>
+        <v>13.92583932710009</v>
       </c>
       <c r="D17">
-        <v>15.03744226351288</v>
+        <v>15.06343932710009</v>
       </c>
       <c r="E17">
-        <v>0.2189999999999999</v>
+        <v>0.3775999999999997</v>
       </c>
       <c r="F17">
-        <v>2.379</v>
+        <v>2.5376</v>
       </c>
       <c r="G17">
         <v>1.4</v>
@@ -2812,28 +2812,28 @@
         <v>2.02</v>
       </c>
       <c r="M17">
-        <v>0.1196637</v>
+        <v>0.12764128</v>
       </c>
       <c r="N17">
-        <v>1.9003363</v>
+        <v>1.89235872</v>
       </c>
       <c r="O17">
-        <v>0.38006726</v>
+        <v>0.3784717440000001</v>
       </c>
       <c r="P17">
-        <v>1.52026904</v>
+        <v>1.513886976</v>
       </c>
       <c r="Q17">
-        <v>1.69026904</v>
+        <v>1.683886976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1135055703650727</v>
+        <v>0.1141703280515241</v>
       </c>
       <c r="T17">
-        <v>0.8110952869092211</v>
+        <v>0.8190589127011624</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.88064133066251</v>
+        <v>15.82560124749611</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1023414755632802</v>
+        <v>0.1021672163162487</v>
       </c>
       <c r="C18">
-        <v>13.92583932710009</v>
+        <v>13.79332643495767</v>
       </c>
       <c r="D18">
-        <v>15.06343932710009</v>
+        <v>15.08952643495767</v>
       </c>
       <c r="E18">
-        <v>0.3775999999999997</v>
+        <v>0.5362</v>
       </c>
       <c r="F18">
-        <v>2.5376</v>
+        <v>2.6962</v>
       </c>
       <c r="G18">
         <v>1.4</v>
@@ -2894,28 +2894,28 @@
         <v>2.02</v>
       </c>
       <c r="M18">
-        <v>0.12764128</v>
+        <v>0.13561886</v>
       </c>
       <c r="N18">
-        <v>1.89235872</v>
+        <v>1.88438114</v>
       </c>
       <c r="O18">
-        <v>0.3784717440000001</v>
+        <v>0.376876228</v>
       </c>
       <c r="P18">
-        <v>1.513886976</v>
+        <v>1.507504912</v>
       </c>
       <c r="Q18">
-        <v>1.683886976</v>
+        <v>1.677504912</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1141703280515241</v>
+        <v>0.1148511039954803</v>
       </c>
       <c r="T18">
-        <v>0.8190589127011624</v>
+        <v>0.8272144330904998</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.82560124749611</v>
+        <v>14.89468352705516</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1021672163162487</v>
+        <v>0.1019929570692171</v>
       </c>
       <c r="C19">
-        <v>13.79332643495767</v>
+        <v>13.66090405571758</v>
       </c>
       <c r="D19">
-        <v>15.08952643495767</v>
+        <v>15.11570405571758</v>
       </c>
       <c r="E19">
-        <v>0.5362</v>
+        <v>0.6948000000000003</v>
       </c>
       <c r="F19">
-        <v>2.6962</v>
+        <v>2.8548</v>
       </c>
       <c r="G19">
         <v>1.4</v>
@@ -2976,28 +2976,28 @@
         <v>2.02</v>
       </c>
       <c r="M19">
-        <v>0.13561886</v>
+        <v>0.14359644</v>
       </c>
       <c r="N19">
-        <v>1.88438114</v>
+        <v>1.87640356</v>
       </c>
       <c r="O19">
-        <v>0.376876228</v>
+        <v>0.375280712</v>
       </c>
       <c r="P19">
-        <v>1.507504912</v>
+        <v>1.501122848</v>
       </c>
       <c r="Q19">
-        <v>1.677504912</v>
+        <v>1.671122848</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1148511039954803</v>
+        <v>0.1155484842307526</v>
       </c>
       <c r="T19">
-        <v>0.8272144330904998</v>
+        <v>0.8355688686112848</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.89468352705516</v>
+        <v>14.06720110888543</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1019929570692171</v>
+        <v>0.1018186978221855</v>
       </c>
       <c r="C20">
-        <v>13.66090405571758</v>
+        <v>13.52857266126941</v>
       </c>
       <c r="D20">
-        <v>15.11570405571759</v>
+        <v>15.14197266126941</v>
       </c>
       <c r="E20">
-        <v>0.6947999999999999</v>
+        <v>0.8533999999999997</v>
       </c>
       <c r="F20">
-        <v>2.8548</v>
+        <v>3.0134</v>
       </c>
       <c r="G20">
         <v>1.4</v>
@@ -3058,28 +3058,28 @@
         <v>2.02</v>
       </c>
       <c r="M20">
-        <v>0.14359644</v>
+        <v>0.15157402</v>
       </c>
       <c r="N20">
-        <v>1.87640356</v>
+        <v>1.86842598</v>
       </c>
       <c r="O20">
-        <v>0.375280712</v>
+        <v>0.3736851960000001</v>
       </c>
       <c r="P20">
-        <v>1.501122848</v>
+        <v>1.494740784</v>
       </c>
       <c r="Q20">
-        <v>1.671122848</v>
+        <v>1.664740784</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1155484842307526</v>
+        <v>0.1162630837310933</v>
       </c>
       <c r="T20">
-        <v>0.8355688686112845</v>
+        <v>0.8441295864906073</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.06720110888543</v>
+        <v>13.32682210315462</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1018186978221855</v>
+        <v>0.101884438575154</v>
       </c>
       <c r="C21">
-        <v>13.52857266126941</v>
+        <v>13.36005189308743</v>
       </c>
       <c r="D21">
-        <v>15.14197266126941</v>
+        <v>15.13205189308743</v>
       </c>
       <c r="E21">
-        <v>0.8533999999999997</v>
+        <v>1.012</v>
       </c>
       <c r="F21">
-        <v>3.0134</v>
+        <v>3.172</v>
       </c>
       <c r="G21">
         <v>1.4</v>
@@ -3140,45 +3140,45 @@
         <v>2.02</v>
       </c>
       <c r="M21">
-        <v>0.15157402</v>
+        <v>0.1643096</v>
       </c>
       <c r="N21">
-        <v>1.86842598</v>
+        <v>1.8556904</v>
       </c>
       <c r="O21">
-        <v>0.3736851960000001</v>
+        <v>0.37113808</v>
       </c>
       <c r="P21">
-        <v>1.494740784</v>
+        <v>1.48455232</v>
       </c>
       <c r="Q21">
-        <v>1.664740784</v>
+        <v>1.65455232</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1162630837310933</v>
+        <v>0.1169955482189425</v>
       </c>
       <c r="T21">
-        <v>0.8441295864906073</v>
+        <v>0.8529043223169129</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.32682210315462</v>
+        <v>12.29386475288115</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.101884438575154</v>
+        <v>0.1017221793281224</v>
       </c>
       <c r="C22">
-        <v>13.36005189308743</v>
+        <v>13.22596161114201</v>
       </c>
       <c r="D22">
-        <v>15.13205189308743</v>
+        <v>15.15656161114201</v>
       </c>
       <c r="E22">
-        <v>1.012</v>
+        <v>1.1706</v>
       </c>
       <c r="F22">
-        <v>3.172</v>
+        <v>3.3306</v>
       </c>
       <c r="G22">
         <v>1.4</v>
@@ -3222,28 +3222,28 @@
         <v>2.02</v>
       </c>
       <c r="M22">
-        <v>0.1643096</v>
+        <v>0.17252508</v>
       </c>
       <c r="N22">
-        <v>1.8556904</v>
+        <v>1.84747492</v>
       </c>
       <c r="O22">
-        <v>0.37113808</v>
+        <v>0.369494984</v>
       </c>
       <c r="P22">
-        <v>1.48455232</v>
+        <v>1.477979936</v>
       </c>
       <c r="Q22">
-        <v>1.65455232</v>
+        <v>1.647979936</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1169955482189425</v>
+        <v>0.1177465561115473</v>
       </c>
       <c r="T22">
-        <v>0.8529043223169129</v>
+        <v>0.8619012033540112</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.29386475288115</v>
+        <v>11.70844262179157</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1017221793281224</v>
+        <v>0.1015599200810908</v>
       </c>
       <c r="C23">
-        <v>13.22596161114201</v>
+        <v>13.09195085586905</v>
       </c>
       <c r="D23">
-        <v>15.15656161114201</v>
+        <v>15.18115085586905</v>
       </c>
       <c r="E23">
-        <v>1.170599999999999</v>
+        <v>1.3292</v>
       </c>
       <c r="F23">
-        <v>3.3306</v>
+        <v>3.4892</v>
       </c>
       <c r="G23">
         <v>1.4</v>
@@ -3304,28 +3304,28 @@
         <v>2.02</v>
       </c>
       <c r="M23">
-        <v>0.17252508</v>
+        <v>0.18074056</v>
       </c>
       <c r="N23">
-        <v>1.84747492</v>
+        <v>1.83925944</v>
       </c>
       <c r="O23">
-        <v>0.369494984</v>
+        <v>0.367851888</v>
       </c>
       <c r="P23">
-        <v>1.477979936</v>
+        <v>1.471407552</v>
       </c>
       <c r="Q23">
-        <v>1.647979936</v>
+        <v>1.641407552</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1177465561115473</v>
+        <v>0.1185168206167831</v>
       </c>
       <c r="T23">
-        <v>0.8619012033540112</v>
+        <v>0.871128773648471</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.70844262179157</v>
+        <v>11.17624068443741</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1015599200810908</v>
+        <v>0.1013976608340593</v>
       </c>
       <c r="C24">
-        <v>13.09195085586905</v>
+        <v>12.95802001495776</v>
       </c>
       <c r="D24">
-        <v>15.18115085586905</v>
+        <v>15.20582001495776</v>
       </c>
       <c r="E24">
-        <v>1.3292</v>
+        <v>1.4878</v>
       </c>
       <c r="F24">
-        <v>3.4892</v>
+        <v>3.6478</v>
       </c>
       <c r="G24">
         <v>1.4</v>
@@ -3386,28 +3386,28 @@
         <v>2.02</v>
       </c>
       <c r="M24">
-        <v>0.18074056</v>
+        <v>0.18895604</v>
       </c>
       <c r="N24">
-        <v>1.83925944</v>
+        <v>1.83104396</v>
       </c>
       <c r="O24">
-        <v>0.367851888</v>
+        <v>0.3662087920000001</v>
       </c>
       <c r="P24">
-        <v>1.471407552</v>
+        <v>1.464835168</v>
       </c>
       <c r="Q24">
-        <v>1.641407552</v>
+        <v>1.634835168</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1185168206167831</v>
+        <v>0.1193070919922848</v>
       </c>
       <c r="T24">
-        <v>0.871128773648471</v>
+        <v>0.8805960210934362</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.17624068443741</v>
+        <v>10.69031717641839</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1013976608340593</v>
+        <v>0.1012354015870277</v>
       </c>
       <c r="C25">
-        <v>12.95802001495776</v>
+        <v>12.82416947862142</v>
       </c>
       <c r="D25">
-        <v>15.20582001495776</v>
+        <v>15.23056947862142</v>
       </c>
       <c r="E25">
-        <v>1.4878</v>
+        <v>1.6464</v>
       </c>
       <c r="F25">
-        <v>3.6478</v>
+        <v>3.8064</v>
       </c>
       <c r="G25">
         <v>1.4</v>
@@ -3468,28 +3468,28 @@
         <v>2.02</v>
       </c>
       <c r="M25">
-        <v>0.18895604</v>
+        <v>0.19717152</v>
       </c>
       <c r="N25">
-        <v>1.83104396</v>
+        <v>1.82282848</v>
       </c>
       <c r="O25">
-        <v>0.3662087920000001</v>
+        <v>0.3645656960000001</v>
       </c>
       <c r="P25">
-        <v>1.464835168</v>
+        <v>1.458262784</v>
       </c>
       <c r="Q25">
-        <v>1.634835168</v>
+        <v>1.628262784</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1193070919922848</v>
+        <v>0.1201181599829312</v>
       </c>
       <c r="T25">
-        <v>0.8805960210934362</v>
+        <v>0.8903124066290583</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.69031717641839</v>
+        <v>10.24488729406762</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1012354015870277</v>
+        <v>0.1010731423399961</v>
       </c>
       <c r="C26">
-        <v>12.82416947862142</v>
+        <v>12.69039963961792</v>
       </c>
       <c r="D26">
-        <v>15.23056947862142</v>
+        <v>15.25539963961792</v>
       </c>
       <c r="E26">
-        <v>1.646399999999999</v>
+        <v>1.805</v>
       </c>
       <c r="F26">
-        <v>3.8064</v>
+        <v>3.965</v>
       </c>
       <c r="G26">
         <v>1.4</v>
@@ -3550,28 +3550,28 @@
         <v>2.02</v>
       </c>
       <c r="M26">
-        <v>0.19717152</v>
+        <v>0.205387</v>
       </c>
       <c r="N26">
-        <v>1.82282848</v>
+        <v>1.814613</v>
       </c>
       <c r="O26">
-        <v>0.3645656960000001</v>
+        <v>0.3629226</v>
       </c>
       <c r="P26">
-        <v>1.458262784</v>
+        <v>1.4516904</v>
       </c>
       <c r="Q26">
-        <v>1.628262784</v>
+        <v>1.6216904</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1201181599829312</v>
+        <v>0.1209508564533281</v>
       </c>
       <c r="T26">
-        <v>0.8903124066290582</v>
+        <v>0.9002878957789636</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.24488729406762</v>
+        <v>9.835091802304918</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1010731423399961</v>
+        <v>0.1012644830929645</v>
       </c>
       <c r="C27">
-        <v>12.69039963961792</v>
+        <v>12.50252774150771</v>
       </c>
       <c r="D27">
-        <v>15.25539963961792</v>
+        <v>15.22612774150771</v>
       </c>
       <c r="E27">
-        <v>1.805</v>
+        <v>1.9636</v>
       </c>
       <c r="F27">
-        <v>3.965</v>
+        <v>4.1236</v>
       </c>
       <c r="G27">
         <v>1.4</v>
@@ -3632,45 +3632,45 @@
         <v>2.02</v>
       </c>
       <c r="M27">
-        <v>0.205387</v>
+        <v>0.2206126</v>
       </c>
       <c r="N27">
-        <v>1.814613</v>
+        <v>1.7993874</v>
       </c>
       <c r="O27">
-        <v>0.3629226</v>
+        <v>0.35987748</v>
       </c>
       <c r="P27">
-        <v>1.4516904</v>
+        <v>1.43950992</v>
       </c>
       <c r="Q27">
-        <v>1.6216904</v>
+        <v>1.60950992</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1209508564533281</v>
+        <v>0.1218060582337359</v>
       </c>
       <c r="T27">
-        <v>0.9002878957789636</v>
+        <v>0.9105329927437313</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.835091802304918</v>
+        <v>9.156321987048791</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1012644830929645</v>
+        <v>0.101115823845933</v>
       </c>
       <c r="C28">
-        <v>12.50252774150771</v>
+        <v>12.3666603426809</v>
       </c>
       <c r="D28">
-        <v>15.22612774150771</v>
+        <v>15.2488603426809</v>
       </c>
       <c r="E28">
-        <v>1.9636</v>
+        <v>2.1222</v>
       </c>
       <c r="F28">
-        <v>4.1236</v>
+        <v>4.2822</v>
       </c>
       <c r="G28">
         <v>1.4</v>
@@ -3714,28 +3714,28 @@
         <v>2.02</v>
       </c>
       <c r="M28">
-        <v>0.2206126</v>
+        <v>0.2290977</v>
       </c>
       <c r="N28">
-        <v>1.7993874</v>
+        <v>1.7909023</v>
       </c>
       <c r="O28">
-        <v>0.35987748</v>
+        <v>0.35818046</v>
       </c>
       <c r="P28">
-        <v>1.43950992</v>
+        <v>1.43272184</v>
       </c>
       <c r="Q28">
-        <v>1.60950992</v>
+        <v>1.60272184</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1218060582337359</v>
+        <v>0.1226846901999082</v>
       </c>
       <c r="T28">
-        <v>0.9105329927437313</v>
+        <v>0.921058777296575</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.156321987048791</v>
+        <v>8.817198950491427</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.101115823845933</v>
+        <v>0.1009671645989014</v>
       </c>
       <c r="C29">
-        <v>12.3666603426809</v>
+        <v>12.23086092487429</v>
       </c>
       <c r="D29">
-        <v>15.2488603426809</v>
+        <v>15.27166092487429</v>
       </c>
       <c r="E29">
-        <v>2.1222</v>
+        <v>2.2808</v>
       </c>
       <c r="F29">
-        <v>4.2822</v>
+        <v>4.4408</v>
       </c>
       <c r="G29">
         <v>1.4</v>
@@ -3796,28 +3796,28 @@
         <v>2.02</v>
       </c>
       <c r="M29">
-        <v>0.2290977</v>
+        <v>0.2375828</v>
       </c>
       <c r="N29">
-        <v>1.7909023</v>
+        <v>1.7824172</v>
       </c>
       <c r="O29">
-        <v>0.35818046</v>
+        <v>0.35648344</v>
       </c>
       <c r="P29">
-        <v>1.43272184</v>
+        <v>1.42593376</v>
       </c>
       <c r="Q29">
-        <v>1.60272184</v>
+        <v>1.59593376</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1226846901999082</v>
+        <v>0.1235877286095853</v>
       </c>
       <c r="T29">
-        <v>0.921058777296575</v>
+        <v>0.9318769447536641</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.817198950491427</v>
+        <v>8.502298987973877</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1009671645989014</v>
+        <v>0.1008185053518698</v>
       </c>
       <c r="C30">
-        <v>12.23086092487429</v>
+        <v>12.0951297934867</v>
       </c>
       <c r="D30">
-        <v>15.27166092487429</v>
+        <v>15.2945297934867</v>
       </c>
       <c r="E30">
-        <v>2.2808</v>
+        <v>2.4394</v>
       </c>
       <c r="F30">
-        <v>4.4408</v>
+        <v>4.5994</v>
       </c>
       <c r="G30">
         <v>1.4</v>
@@ -3878,28 +3878,28 @@
         <v>2.02</v>
       </c>
       <c r="M30">
-        <v>0.2375828</v>
+        <v>0.2460679</v>
       </c>
       <c r="N30">
-        <v>1.7824172</v>
+        <v>1.7739321</v>
       </c>
       <c r="O30">
-        <v>0.35648344</v>
+        <v>0.35478642</v>
       </c>
       <c r="P30">
-        <v>1.42593376</v>
+        <v>1.41914568</v>
       </c>
       <c r="Q30">
-        <v>1.59593376</v>
+        <v>1.58914568</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1235877286095853</v>
+        <v>0.1245162047209434</v>
       </c>
       <c r="T30">
-        <v>0.9318769447536641</v>
+        <v>0.9429998493222206</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.502298987973877</v>
+        <v>8.209116264250639</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1008185053518698</v>
+        <v>0.1006698461048383</v>
       </c>
       <c r="C31">
-        <v>12.0951297934867</v>
+        <v>11.95946725574898</v>
       </c>
       <c r="D31">
-        <v>15.2945297934867</v>
+        <v>15.31746725574898</v>
       </c>
       <c r="E31">
-        <v>2.439399999999999</v>
+        <v>2.598</v>
       </c>
       <c r="F31">
-        <v>4.599399999999999</v>
+        <v>4.758</v>
       </c>
       <c r="G31">
         <v>1.4</v>
@@ -3960,28 +3960,28 @@
         <v>2.02</v>
       </c>
       <c r="M31">
-        <v>0.2460679</v>
+        <v>0.254553</v>
       </c>
       <c r="N31">
-        <v>1.7739321</v>
+        <v>1.765447</v>
       </c>
       <c r="O31">
-        <v>0.35478642</v>
+        <v>0.3530894</v>
       </c>
       <c r="P31">
-        <v>1.41914568</v>
+        <v>1.4123576</v>
       </c>
       <c r="Q31">
-        <v>1.58914568</v>
+        <v>1.5823576</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1245162047209434</v>
+        <v>0.1254712087211975</v>
       </c>
       <c r="T31">
-        <v>0.9429998493222206</v>
+        <v>0.9544405511641645</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.209116264250643</v>
+        <v>7.935479055442285</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1006698461048383</v>
+        <v>0.1005211868578067</v>
       </c>
       <c r="C32">
-        <v>11.95946725574898</v>
+        <v>11.82387362073778</v>
       </c>
       <c r="D32">
-        <v>15.31746725574898</v>
+        <v>15.34047362073778</v>
       </c>
       <c r="E32">
-        <v>2.598</v>
+        <v>2.7566</v>
       </c>
       <c r="F32">
-        <v>4.758</v>
+        <v>4.9166</v>
       </c>
       <c r="G32">
         <v>1.4</v>
@@ -4042,28 +4042,28 @@
         <v>2.02</v>
       </c>
       <c r="M32">
-        <v>0.254553</v>
+        <v>0.2630381</v>
       </c>
       <c r="N32">
-        <v>1.765447</v>
+        <v>1.7569619</v>
       </c>
       <c r="O32">
-        <v>0.3530894</v>
+        <v>0.3513923800000001</v>
       </c>
       <c r="P32">
-        <v>1.4123576</v>
+        <v>1.40556952</v>
       </c>
       <c r="Q32">
-        <v>1.5823576</v>
+        <v>1.57556952</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1254712087211975</v>
+        <v>0.1264538939968213</v>
       </c>
       <c r="T32">
-        <v>0.9544405511641645</v>
+        <v>0.9662128675522516</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.935479055442285</v>
+        <v>7.679495860105438</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1005211868578067</v>
+        <v>0.1005773276107751</v>
       </c>
       <c r="C33">
-        <v>11.82387362073778</v>
+        <v>11.65657721389367</v>
       </c>
       <c r="D33">
-        <v>15.34047362073778</v>
+        <v>15.33177721389367</v>
       </c>
       <c r="E33">
-        <v>2.7566</v>
+        <v>2.9152</v>
       </c>
       <c r="F33">
-        <v>4.9166</v>
+        <v>5.0752</v>
       </c>
       <c r="G33">
         <v>1.4</v>
@@ -4124,45 +4124,45 @@
         <v>2.02</v>
       </c>
       <c r="M33">
-        <v>0.2630381</v>
+        <v>0.27558336</v>
       </c>
       <c r="N33">
-        <v>1.7569619</v>
+        <v>1.74441664</v>
       </c>
       <c r="O33">
-        <v>0.3513923800000001</v>
+        <v>0.348883328</v>
       </c>
       <c r="P33">
-        <v>1.40556952</v>
+        <v>1.395533312</v>
       </c>
       <c r="Q33">
-        <v>1.57556952</v>
+        <v>1.565533312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1264538939968213</v>
+        <v>0.1274654817805516</v>
       </c>
       <c r="T33">
-        <v>0.9662128675522516</v>
+        <v>0.9783314285399883</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.679495860105438</v>
+        <v>7.329905550175454</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1005773276107751</v>
+        <v>0.1004350683637436</v>
       </c>
       <c r="C34">
-        <v>11.65657721389367</v>
+        <v>11.52003287919422</v>
       </c>
       <c r="D34">
-        <v>15.33177721389367</v>
+        <v>15.35383287919422</v>
       </c>
       <c r="E34">
-        <v>2.9152</v>
+        <v>3.0738</v>
       </c>
       <c r="F34">
-        <v>5.0752</v>
+        <v>5.2338</v>
       </c>
       <c r="G34">
         <v>1.4</v>
@@ -4206,28 +4206,28 @@
         <v>2.02</v>
       </c>
       <c r="M34">
-        <v>0.27558336</v>
+        <v>0.28419534</v>
       </c>
       <c r="N34">
-        <v>1.74441664</v>
+        <v>1.73580466</v>
       </c>
       <c r="O34">
-        <v>0.348883328</v>
+        <v>0.347160932</v>
       </c>
       <c r="P34">
-        <v>1.395533312</v>
+        <v>1.388643728</v>
       </c>
       <c r="Q34">
-        <v>1.565533312</v>
+        <v>1.558643728</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1274654817805516</v>
+        <v>0.1285072662145426</v>
       </c>
       <c r="T34">
-        <v>0.9783314285399883</v>
+        <v>0.9908117376169113</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.329905550175454</v>
+        <v>7.107787200170136</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1004350683637436</v>
+        <v>0.100292809116712</v>
       </c>
       <c r="C35">
-        <v>11.52003287919422</v>
+        <v>11.3835520926619</v>
       </c>
       <c r="D35">
-        <v>15.35383287919422</v>
+        <v>15.3759520926619</v>
       </c>
       <c r="E35">
-        <v>3.0738</v>
+        <v>3.2324</v>
       </c>
       <c r="F35">
-        <v>5.2338</v>
+        <v>5.3924</v>
       </c>
       <c r="G35">
         <v>1.4</v>
@@ -4288,28 +4288,28 @@
         <v>2.02</v>
       </c>
       <c r="M35">
-        <v>0.28419534</v>
+        <v>0.29280732</v>
       </c>
       <c r="N35">
-        <v>1.73580466</v>
+        <v>1.72719268</v>
       </c>
       <c r="O35">
-        <v>0.347160932</v>
+        <v>0.345438536</v>
       </c>
       <c r="P35">
-        <v>1.388643728</v>
+        <v>1.381754144</v>
       </c>
       <c r="Q35">
-        <v>1.558643728</v>
+        <v>1.551754144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1285072662145426</v>
+        <v>0.129580619873806</v>
       </c>
       <c r="T35">
-        <v>0.9908117376169113</v>
+        <v>1.003670237877983</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.107787200170136</v>
+        <v>6.898734635459249</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.100292809116712</v>
+        <v>0.1001505498696804</v>
       </c>
       <c r="C36">
-        <v>11.3835520926619</v>
+        <v>11.2471351293414</v>
       </c>
       <c r="D36">
-        <v>15.3759520926619</v>
+        <v>15.3981351293414</v>
       </c>
       <c r="E36">
-        <v>3.2324</v>
+        <v>3.391</v>
       </c>
       <c r="F36">
-        <v>5.3924</v>
+        <v>5.551</v>
       </c>
       <c r="G36">
         <v>1.4</v>
@@ -4370,28 +4370,28 @@
         <v>2.02</v>
       </c>
       <c r="M36">
-        <v>0.29280732</v>
+        <v>0.3014193</v>
       </c>
       <c r="N36">
-        <v>1.72719268</v>
+        <v>1.7185807</v>
       </c>
       <c r="O36">
-        <v>0.345438536</v>
+        <v>0.34371614</v>
       </c>
       <c r="P36">
-        <v>1.381754144</v>
+        <v>1.37486456</v>
       </c>
       <c r="Q36">
-        <v>1.551754144</v>
+        <v>1.54486456</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.129580619873806</v>
+        <v>0.1306869997995083</v>
       </c>
       <c r="T36">
-        <v>1.003670237877983</v>
+        <v>1.016924384300935</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.898734635459249</v>
+        <v>6.701627931588986</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1001505498696804</v>
+        <v>0.1000082906226488</v>
       </c>
       <c r="C37">
-        <v>11.2471351293414</v>
+        <v>11.11078226586694</v>
       </c>
       <c r="D37">
-        <v>15.3981351293414</v>
+        <v>15.42038226586694</v>
       </c>
       <c r="E37">
-        <v>3.391</v>
+        <v>3.549600000000001</v>
       </c>
       <c r="F37">
-        <v>5.551</v>
+        <v>5.709600000000001</v>
       </c>
       <c r="G37">
         <v>1.4</v>
@@ -4452,28 +4452,28 @@
         <v>2.02</v>
       </c>
       <c r="M37">
-        <v>0.3014193</v>
+        <v>0.3100312800000001</v>
       </c>
       <c r="N37">
-        <v>1.7185807</v>
+        <v>1.70996872</v>
       </c>
       <c r="O37">
-        <v>0.34371614</v>
+        <v>0.341993744</v>
       </c>
       <c r="P37">
-        <v>1.37486456</v>
+        <v>1.367974976</v>
       </c>
       <c r="Q37">
-        <v>1.54486456</v>
+        <v>1.537974976</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1306869997995083</v>
+        <v>0.1318279540978888</v>
       </c>
       <c r="T37">
-        <v>1.016924384300935</v>
+        <v>1.030592722799603</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.701627931588986</v>
+        <v>6.515471600155957</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1000082906226488</v>
+        <v>0.09986603137561727</v>
       </c>
       <c r="C38">
-        <v>11.11078226586694</v>
+        <v>10.97449378047377</v>
       </c>
       <c r="D38">
-        <v>15.42038226586694</v>
+        <v>15.44269378047377</v>
       </c>
       <c r="E38">
-        <v>3.5496</v>
+        <v>3.7082</v>
       </c>
       <c r="F38">
-        <v>5.7096</v>
+        <v>5.8682</v>
       </c>
       <c r="G38">
         <v>1.4</v>
@@ -4534,28 +4534,28 @@
         <v>2.02</v>
       </c>
       <c r="M38">
-        <v>0.31003128</v>
+        <v>0.31864326</v>
       </c>
       <c r="N38">
-        <v>1.70996872</v>
+        <v>1.70135674</v>
       </c>
       <c r="O38">
-        <v>0.341993744</v>
+        <v>0.340271348</v>
       </c>
       <c r="P38">
-        <v>1.367974976</v>
+        <v>1.361085392</v>
       </c>
       <c r="Q38">
-        <v>1.537974976</v>
+        <v>1.531085392</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1318279540978888</v>
+        <v>0.1330051291676465</v>
       </c>
       <c r="T38">
-        <v>1.030592722799603</v>
+        <v>1.044694976806166</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.515471600155958</v>
+        <v>6.339377773124717</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09986603137561727</v>
+        <v>0.09972377212858567</v>
       </c>
       <c r="C39">
-        <v>10.97449378047377</v>
+        <v>10.83826995300979</v>
       </c>
       <c r="D39">
-        <v>15.44269378047377</v>
+        <v>15.46506995300979</v>
       </c>
       <c r="E39">
-        <v>3.7082</v>
+        <v>3.8668</v>
       </c>
       <c r="F39">
-        <v>5.8682</v>
+        <v>6.0268</v>
       </c>
       <c r="G39">
         <v>1.4</v>
@@ -4616,28 +4616,28 @@
         <v>2.02</v>
       </c>
       <c r="M39">
-        <v>0.31864326</v>
+        <v>0.32725524</v>
       </c>
       <c r="N39">
-        <v>1.70135674</v>
+        <v>1.69274476</v>
       </c>
       <c r="O39">
-        <v>0.340271348</v>
+        <v>0.338548952</v>
       </c>
       <c r="P39">
-        <v>1.361085392</v>
+        <v>1.354195808</v>
       </c>
       <c r="Q39">
-        <v>1.531085392</v>
+        <v>1.524195808</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1330051291676465</v>
+        <v>0.1342202776267511</v>
       </c>
       <c r="T39">
-        <v>1.044694976806166</v>
+        <v>1.059252142232295</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.339377773124717</v>
+        <v>6.172552042253013</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09972377212858567</v>
+        <v>0.09989351288155413</v>
       </c>
       <c r="C40">
-        <v>10.83826995300979</v>
+        <v>10.65297863319342</v>
       </c>
       <c r="D40">
-        <v>15.46506995300979</v>
+        <v>15.43837863319342</v>
       </c>
       <c r="E40">
-        <v>3.8668</v>
+        <v>4.025399999999999</v>
       </c>
       <c r="F40">
-        <v>6.0268</v>
+        <v>6.1854</v>
       </c>
       <c r="G40">
         <v>1.4</v>
@@ -4698,45 +4698,45 @@
         <v>2.02</v>
       </c>
       <c r="M40">
-        <v>0.32725524</v>
+        <v>0.34205262</v>
       </c>
       <c r="N40">
-        <v>1.69274476</v>
+        <v>1.67794738</v>
       </c>
       <c r="O40">
-        <v>0.338548952</v>
+        <v>0.335589476</v>
       </c>
       <c r="P40">
-        <v>1.354195808</v>
+        <v>1.342357904</v>
       </c>
       <c r="Q40">
-        <v>1.524195808</v>
+        <v>1.512357904</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1342202776267511</v>
+        <v>0.1354752670189412</v>
       </c>
       <c r="T40">
-        <v>1.059252142232295</v>
+        <v>1.074286591770756</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.2</v>
       </c>
       <c r="W40">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.172552042253013</v>
+        <v>5.905524126667997</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09989351288155413</v>
+        <v>0.09975925363452254</v>
       </c>
       <c r="C41">
-        <v>10.65297863319342</v>
+        <v>10.51548294562436</v>
       </c>
       <c r="D41">
-        <v>15.43837863319342</v>
+        <v>15.45948294562436</v>
       </c>
       <c r="E41">
-        <v>4.025399999999999</v>
+        <v>4.184</v>
       </c>
       <c r="F41">
-        <v>6.1854</v>
+        <v>6.344</v>
       </c>
       <c r="G41">
         <v>1.4</v>
@@ -4780,28 +4780,28 @@
         <v>2.02</v>
       </c>
       <c r="M41">
-        <v>0.34205262</v>
+        <v>0.3508232</v>
       </c>
       <c r="N41">
-        <v>1.67794738</v>
+        <v>1.6691768</v>
       </c>
       <c r="O41">
-        <v>0.335589476</v>
+        <v>0.33383536</v>
       </c>
       <c r="P41">
-        <v>1.342357904</v>
+        <v>1.33534144</v>
       </c>
       <c r="Q41">
-        <v>1.512357904</v>
+        <v>1.50534144</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1354752670189412</v>
+        <v>0.1367720893908709</v>
       </c>
       <c r="T41">
-        <v>1.074286591770756</v>
+        <v>1.089822189627166</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.905524126667997</v>
+        <v>5.757886023501296</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09975925363452254</v>
+        <v>0.09962499438749098</v>
       </c>
       <c r="C42">
-        <v>10.51548294562436</v>
+        <v>10.37804503636213</v>
       </c>
       <c r="D42">
-        <v>15.45948294562436</v>
+        <v>15.48064503636214</v>
       </c>
       <c r="E42">
-        <v>4.184</v>
+        <v>4.3426</v>
       </c>
       <c r="F42">
-        <v>6.344</v>
+        <v>6.5026</v>
       </c>
       <c r="G42">
         <v>1.4</v>
@@ -4862,28 +4862,28 @@
         <v>2.02</v>
       </c>
       <c r="M42">
-        <v>0.3508232</v>
+        <v>0.35959378</v>
       </c>
       <c r="N42">
-        <v>1.6691768</v>
+        <v>1.66040622</v>
       </c>
       <c r="O42">
-        <v>0.33383536</v>
+        <v>0.3320812440000001</v>
       </c>
       <c r="P42">
-        <v>1.33534144</v>
+        <v>1.328324976</v>
       </c>
       <c r="Q42">
-        <v>1.50534144</v>
+        <v>1.498324976</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1367720893908709</v>
+        <v>0.1381128718432051</v>
       </c>
       <c r="T42">
-        <v>1.089822189627166</v>
+        <v>1.105884417919387</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.757886023501296</v>
+        <v>5.617449779025654</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09962499438749098</v>
+        <v>0.09949073514045942</v>
       </c>
       <c r="C43">
-        <v>10.37804503636213</v>
+        <v>10.24066514300574</v>
       </c>
       <c r="D43">
-        <v>15.48064503636214</v>
+        <v>15.50186514300574</v>
       </c>
       <c r="E43">
-        <v>4.3426</v>
+        <v>4.5012</v>
       </c>
       <c r="F43">
-        <v>6.5026</v>
+        <v>6.6612</v>
       </c>
       <c r="G43">
         <v>1.4</v>
@@ -4944,28 +4944,28 @@
         <v>2.02</v>
       </c>
       <c r="M43">
-        <v>0.35959378</v>
+        <v>0.36836436</v>
       </c>
       <c r="N43">
-        <v>1.66040622</v>
+        <v>1.65163564</v>
       </c>
       <c r="O43">
-        <v>0.3320812440000001</v>
+        <v>0.330327128</v>
       </c>
       <c r="P43">
-        <v>1.328324976</v>
+        <v>1.321308512</v>
       </c>
       <c r="Q43">
-        <v>1.498324976</v>
+        <v>1.491308512</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1381128718432051</v>
+        <v>0.1394998881732059</v>
       </c>
       <c r="T43">
-        <v>1.105884417919387</v>
+        <v>1.122500516152719</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.617449779025654</v>
+        <v>5.483700974763139</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09949073514045942</v>
+        <v>0.09935647589342786</v>
       </c>
       <c r="C44">
-        <v>10.24066514300574</v>
+        <v>10.10334350445869</v>
       </c>
       <c r="D44">
-        <v>15.50186514300574</v>
+        <v>15.52314350445869</v>
       </c>
       <c r="E44">
-        <v>4.501199999999999</v>
+        <v>4.6598</v>
       </c>
       <c r="F44">
-        <v>6.661199999999999</v>
+        <v>6.8198</v>
       </c>
       <c r="G44">
         <v>1.4</v>
@@ -5026,28 +5026,28 @@
         <v>2.02</v>
       </c>
       <c r="M44">
-        <v>0.3683643599999999</v>
+        <v>0.37713494</v>
       </c>
       <c r="N44">
-        <v>1.65163564</v>
+        <v>1.64286506</v>
       </c>
       <c r="O44">
-        <v>0.330327128</v>
+        <v>0.3285730120000001</v>
       </c>
       <c r="P44">
-        <v>1.321308512</v>
+        <v>1.314292048</v>
       </c>
       <c r="Q44">
-        <v>1.491308512</v>
+        <v>1.484292048</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1394998881732059</v>
+        <v>0.1409355717428559</v>
       </c>
       <c r="T44">
-        <v>1.122500516152719</v>
+        <v>1.139699635376694</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.48370097476314</v>
+        <v>5.356173045117485</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09935647589342786</v>
+        <v>0.09922221664639627</v>
       </c>
       <c r="C45">
-        <v>10.10334350445869</v>
+        <v>9.96608036093803</v>
       </c>
       <c r="D45">
-        <v>15.52314350445869</v>
+        <v>15.54448036093803</v>
       </c>
       <c r="E45">
-        <v>4.6598</v>
+        <v>4.8184</v>
       </c>
       <c r="F45">
-        <v>6.8198</v>
+        <v>6.9784</v>
       </c>
       <c r="G45">
         <v>1.4</v>
@@ -5108,28 +5108,28 @@
         <v>2.02</v>
       </c>
       <c r="M45">
-        <v>0.37713494</v>
+        <v>0.38590552</v>
       </c>
       <c r="N45">
-        <v>1.64286506</v>
+        <v>1.63409448</v>
       </c>
       <c r="O45">
-        <v>0.3285730120000001</v>
+        <v>0.326818896</v>
       </c>
       <c r="P45">
-        <v>1.314292048</v>
+        <v>1.307275584</v>
       </c>
       <c r="Q45">
-        <v>1.484292048</v>
+        <v>1.477275584</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1409355717428559</v>
+        <v>0.1424225297257076</v>
       </c>
       <c r="T45">
-        <v>1.139699635376694</v>
+        <v>1.157513008858668</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.356173045117485</v>
+        <v>5.234441839546633</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09922221664639627</v>
+        <v>0.09908795739936471</v>
       </c>
       <c r="C46">
-        <v>9.96608036093803</v>
+        <v>9.828875953983335</v>
       </c>
       <c r="D46">
-        <v>15.54448036093803</v>
+        <v>15.56587595398334</v>
       </c>
       <c r="E46">
-        <v>4.8184</v>
+        <v>4.976999999999999</v>
       </c>
       <c r="F46">
-        <v>6.9784</v>
+        <v>7.137</v>
       </c>
       <c r="G46">
         <v>1.4</v>
@@ -5190,28 +5190,28 @@
         <v>2.02</v>
       </c>
       <c r="M46">
-        <v>0.38590552</v>
+        <v>0.3946761</v>
       </c>
       <c r="N46">
-        <v>1.63409448</v>
+        <v>1.6253239</v>
       </c>
       <c r="O46">
-        <v>0.326818896</v>
+        <v>0.3250647800000001</v>
       </c>
       <c r="P46">
-        <v>1.307275584</v>
+        <v>1.30025912</v>
       </c>
       <c r="Q46">
-        <v>1.477275584</v>
+        <v>1.47025912</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1424225297257076</v>
+        <v>0.1439635589079358</v>
       </c>
       <c r="T46">
-        <v>1.157513008858668</v>
+        <v>1.17597414137635</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.234441839546633</v>
+        <v>5.118120909778931</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09908795739936471</v>
+        <v>0.09895369815233314</v>
       </c>
       <c r="C47">
-        <v>9.828875953983335</v>
+        <v>9.691730526465864</v>
       </c>
       <c r="D47">
-        <v>15.56587595398334</v>
+        <v>15.58733052646586</v>
       </c>
       <c r="E47">
-        <v>4.976999999999999</v>
+        <v>5.1356</v>
       </c>
       <c r="F47">
-        <v>7.137</v>
+        <v>7.2956</v>
       </c>
       <c r="G47">
         <v>1.4</v>
@@ -5272,28 +5272,28 @@
         <v>2.02</v>
       </c>
       <c r="M47">
-        <v>0.3946761</v>
+        <v>0.4034466800000001</v>
       </c>
       <c r="N47">
-        <v>1.6253239</v>
+        <v>1.61655332</v>
       </c>
       <c r="O47">
-        <v>0.3250647800000001</v>
+        <v>0.323310664</v>
       </c>
       <c r="P47">
-        <v>1.30025912</v>
+        <v>1.293242656</v>
       </c>
       <c r="Q47">
-        <v>1.47025912</v>
+        <v>1.463242656</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1439635589079358</v>
+        <v>0.1455616632450613</v>
       </c>
       <c r="T47">
-        <v>1.17597414137635</v>
+        <v>1.195119019542835</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.118120909778931</v>
+        <v>5.006857411740257</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09895369815233314</v>
+        <v>0.09881943890530157</v>
       </c>
       <c r="C48">
-        <v>9.691730526465864</v>
+        <v>9.554644322597717</v>
       </c>
       <c r="D48">
-        <v>15.58733052646586</v>
+        <v>15.60884432259772</v>
       </c>
       <c r="E48">
-        <v>5.1356</v>
+        <v>5.2942</v>
       </c>
       <c r="F48">
-        <v>7.2956</v>
+        <v>7.4542</v>
       </c>
       <c r="G48">
         <v>1.4</v>
@@ -5354,28 +5354,28 @@
         <v>2.02</v>
       </c>
       <c r="M48">
-        <v>0.4034466800000001</v>
+        <v>0.41221726</v>
       </c>
       <c r="N48">
-        <v>1.61655332</v>
+        <v>1.60778274</v>
       </c>
       <c r="O48">
-        <v>0.323310664</v>
+        <v>0.321556548</v>
       </c>
       <c r="P48">
-        <v>1.293242656</v>
+        <v>1.286226192</v>
       </c>
       <c r="Q48">
-        <v>1.463242656</v>
+        <v>1.456226192</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1455616632450613</v>
+        <v>0.1472200734062294</v>
       </c>
       <c r="T48">
-        <v>1.195119019542835</v>
+        <v>1.214986345942018</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.006857411740257</v>
+        <v>4.900328530639401</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09881943890530157</v>
+        <v>0.09868517965827001</v>
       </c>
       <c r="C49">
-        <v>9.554644322597717</v>
+        <v>9.417617587941109</v>
       </c>
       <c r="D49">
-        <v>15.60884432259772</v>
+        <v>15.63041758794111</v>
       </c>
       <c r="E49">
-        <v>5.2942</v>
+        <v>5.4528</v>
       </c>
       <c r="F49">
-        <v>7.4542</v>
+        <v>7.6128</v>
       </c>
       <c r="G49">
         <v>1.4</v>
@@ -5436,28 +5436,28 @@
         <v>2.02</v>
       </c>
       <c r="M49">
-        <v>0.41221726</v>
+        <v>0.42098784</v>
       </c>
       <c r="N49">
-        <v>1.60778274</v>
+        <v>1.59901216</v>
       </c>
       <c r="O49">
-        <v>0.321556548</v>
+        <v>0.319802432</v>
       </c>
       <c r="P49">
-        <v>1.286226192</v>
+        <v>1.279209728</v>
       </c>
       <c r="Q49">
-        <v>1.456226192</v>
+        <v>1.449209728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1472200734062294</v>
+        <v>0.1489422685735961</v>
       </c>
       <c r="T49">
-        <v>1.214986345942018</v>
+        <v>1.23561780027963</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.900328530639401</v>
+        <v>4.798238352917747</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09868517965826999</v>
+        <v>0.09855092041123842</v>
       </c>
       <c r="C50">
-        <v>9.417617587941113</v>
+        <v>9.280650569417741</v>
       </c>
       <c r="D50">
-        <v>15.63041758794111</v>
+        <v>15.65205056941774</v>
       </c>
       <c r="E50">
-        <v>5.452799999999999</v>
+        <v>5.6114</v>
       </c>
       <c r="F50">
-        <v>7.612799999999999</v>
+        <v>7.7714</v>
       </c>
       <c r="G50">
         <v>1.4</v>
@@ -5518,28 +5518,28 @@
         <v>2.02</v>
       </c>
       <c r="M50">
-        <v>0.4209878399999999</v>
+        <v>0.42975842</v>
       </c>
       <c r="N50">
-        <v>1.59901216</v>
+        <v>1.59024158</v>
       </c>
       <c r="O50">
-        <v>0.319802432</v>
+        <v>0.3180483160000001</v>
       </c>
       <c r="P50">
-        <v>1.279209728</v>
+        <v>1.272193264</v>
       </c>
       <c r="Q50">
-        <v>1.449209728</v>
+        <v>1.442193264</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1489422685735961</v>
+        <v>0.1507320008063498</v>
       </c>
       <c r="T50">
-        <v>1.23561780027963</v>
+        <v>1.257058331257934</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.798238352917748</v>
+        <v>4.700315121225549</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09855092041123842</v>
+        <v>0.09841666116420685</v>
       </c>
       <c r="C51">
-        <v>9.280650569417741</v>
+        <v>9.143743515318164</v>
       </c>
       <c r="D51">
-        <v>15.65205056941774</v>
+        <v>15.67374351531817</v>
       </c>
       <c r="E51">
-        <v>5.6114</v>
+        <v>5.77</v>
       </c>
       <c r="F51">
-        <v>7.7714</v>
+        <v>7.93</v>
       </c>
       <c r="G51">
         <v>1.4</v>
@@ -5600,28 +5600,28 @@
         <v>2.02</v>
       </c>
       <c r="M51">
-        <v>0.42975842</v>
+        <v>0.438529</v>
       </c>
       <c r="N51">
-        <v>1.59024158</v>
+        <v>1.581471</v>
       </c>
       <c r="O51">
-        <v>0.3180483160000001</v>
+        <v>0.3162942</v>
       </c>
       <c r="P51">
-        <v>1.272193264</v>
+        <v>1.2651768</v>
       </c>
       <c r="Q51">
-        <v>1.442193264</v>
+        <v>1.4351768</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1507320008063498</v>
+        <v>0.1525933223284137</v>
       </c>
       <c r="T51">
-        <v>1.257058331257934</v>
+        <v>1.279356483475369</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.700315121225549</v>
+        <v>4.606308818801037</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09841666116420685</v>
+        <v>0.09828240191717527</v>
       </c>
       <c r="C52">
-        <v>9.143743515318164</v>
+        <v>9.006896675311342</v>
       </c>
       <c r="D52">
-        <v>15.67374351531817</v>
+        <v>15.69549667531134</v>
       </c>
       <c r="E52">
-        <v>5.77</v>
+        <v>5.928599999999999</v>
       </c>
       <c r="F52">
-        <v>7.93</v>
+        <v>8.0886</v>
       </c>
       <c r="G52">
         <v>1.4</v>
@@ -5682,28 +5682,28 @@
         <v>2.02</v>
       </c>
       <c r="M52">
-        <v>0.438529</v>
+        <v>0.44729958</v>
       </c>
       <c r="N52">
-        <v>1.581471</v>
+        <v>1.57270042</v>
       </c>
       <c r="O52">
-        <v>0.3162942</v>
+        <v>0.3145400840000001</v>
       </c>
       <c r="P52">
-        <v>1.2651768</v>
+        <v>1.258160336</v>
       </c>
       <c r="Q52">
-        <v>1.4351768</v>
+        <v>1.428160336</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1525933223284137</v>
+        <v>0.1545306161575006</v>
       </c>
       <c r="T52">
-        <v>1.279356483475369</v>
+        <v>1.302564764354741</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.606308818801037</v>
+        <v>4.515989038040233</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09828240191717527</v>
+        <v>0.09918814267014371</v>
       </c>
       <c r="C53">
-        <v>9.006896675311342</v>
+        <v>8.702704828395639</v>
       </c>
       <c r="D53">
-        <v>15.69549667531134</v>
+        <v>15.54990482839564</v>
       </c>
       <c r="E53">
-        <v>5.928599999999999</v>
+        <v>6.087199999999999</v>
       </c>
       <c r="F53">
-        <v>8.0886</v>
+        <v>8.247199999999999</v>
       </c>
       <c r="G53">
         <v>1.4</v>
@@ -5764,45 +5764,45 @@
         <v>2.02</v>
       </c>
       <c r="M53">
-        <v>0.44729958</v>
+        <v>0.47668816</v>
       </c>
       <c r="N53">
-        <v>1.57270042</v>
+        <v>1.54331184</v>
       </c>
       <c r="O53">
-        <v>0.3145400840000001</v>
+        <v>0.308662368</v>
       </c>
       <c r="P53">
-        <v>1.258160336</v>
+        <v>1.234649472</v>
       </c>
       <c r="Q53">
-        <v>1.428160336</v>
+        <v>1.404649472</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1545306161575006</v>
+        <v>0.1565486305627994</v>
       </c>
       <c r="T53">
-        <v>1.302564764354741</v>
+        <v>1.32674005693742</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.515989038040233</v>
+        <v>4.237571161826214</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09918814267014371</v>
+        <v>0.09907388342311213</v>
       </c>
       <c r="C54">
-        <v>8.702704828395639</v>
+        <v>8.562322198132041</v>
       </c>
       <c r="D54">
-        <v>15.54990482839564</v>
+        <v>15.56812219813204</v>
       </c>
       <c r="E54">
-        <v>6.087199999999999</v>
+        <v>6.245799999999999</v>
       </c>
       <c r="F54">
-        <v>8.247199999999999</v>
+        <v>8.405799999999999</v>
       </c>
       <c r="G54">
         <v>1.4</v>
@@ -5846,28 +5846,28 @@
         <v>2.02</v>
       </c>
       <c r="M54">
-        <v>0.47668816</v>
+        <v>0.48585524</v>
       </c>
       <c r="N54">
-        <v>1.54331184</v>
+        <v>1.53414476</v>
       </c>
       <c r="O54">
-        <v>0.308662368</v>
+        <v>0.306828952</v>
       </c>
       <c r="P54">
-        <v>1.234649472</v>
+        <v>1.227315808</v>
       </c>
       <c r="Q54">
-        <v>1.404649472</v>
+        <v>1.397315808</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1565486305627994</v>
+        <v>0.1586525179215152</v>
       </c>
       <c r="T54">
-        <v>1.32674005693742</v>
+        <v>1.351944085374681</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.237571161826214</v>
+        <v>4.157616988961568</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09907388342311213</v>
+        <v>0.09895962417608056</v>
       </c>
       <c r="C55">
-        <v>8.562322198132041</v>
+        <v>8.421982302769068</v>
       </c>
       <c r="D55">
-        <v>15.56812219813204</v>
+        <v>15.58638230276907</v>
       </c>
       <c r="E55">
-        <v>6.245799999999999</v>
+        <v>6.404400000000001</v>
       </c>
       <c r="F55">
-        <v>8.405799999999999</v>
+        <v>8.564400000000001</v>
       </c>
       <c r="G55">
         <v>1.4</v>
@@ -5928,28 +5928,28 @@
         <v>2.02</v>
       </c>
       <c r="M55">
-        <v>0.48585524</v>
+        <v>0.4950223200000001</v>
       </c>
       <c r="N55">
-        <v>1.53414476</v>
+        <v>1.52497768</v>
       </c>
       <c r="O55">
-        <v>0.306828952</v>
+        <v>0.304995536</v>
       </c>
       <c r="P55">
-        <v>1.227315808</v>
+        <v>1.219982144</v>
       </c>
       <c r="Q55">
-        <v>1.397315808</v>
+        <v>1.389982144</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1586525179215152</v>
+        <v>0.1608478786436534</v>
       </c>
       <c r="T55">
-        <v>1.351944085374681</v>
+        <v>1.378243941135301</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.157616988961568</v>
+        <v>4.080624081758575</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09895962417608056</v>
+        <v>0.098845364929049</v>
       </c>
       <c r="C56">
-        <v>8.421982302769068</v>
+        <v>8.281685292856706</v>
       </c>
       <c r="D56">
-        <v>15.58638230276907</v>
+        <v>15.60468529285671</v>
       </c>
       <c r="E56">
-        <v>6.404400000000001</v>
+        <v>6.563000000000001</v>
       </c>
       <c r="F56">
-        <v>8.564400000000001</v>
+        <v>8.723000000000001</v>
       </c>
       <c r="G56">
         <v>1.4</v>
@@ -6010,28 +6010,28 @@
         <v>2.02</v>
       </c>
       <c r="M56">
-        <v>0.4950223200000001</v>
+        <v>0.5041894000000001</v>
       </c>
       <c r="N56">
-        <v>1.52497768</v>
+        <v>1.5158106</v>
       </c>
       <c r="O56">
-        <v>0.304995536</v>
+        <v>0.30316212</v>
       </c>
       <c r="P56">
-        <v>1.219982144</v>
+        <v>1.21264848</v>
       </c>
       <c r="Q56">
-        <v>1.389982144</v>
+        <v>1.38264848</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1608478786436534</v>
+        <v>0.1631408109534422</v>
       </c>
       <c r="T56">
-        <v>1.378243941135301</v>
+        <v>1.405712679374171</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.080624081758575</v>
+        <v>4.006430916635692</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.098845364929049</v>
+        <v>0.1002991056820174</v>
       </c>
       <c r="C57">
-        <v>8.281685292856706</v>
+        <v>7.893371721782108</v>
       </c>
       <c r="D57">
-        <v>15.60468529285671</v>
+        <v>15.37497172178211</v>
       </c>
       <c r="E57">
-        <v>6.563000000000001</v>
+        <v>6.7216</v>
       </c>
       <c r="F57">
-        <v>8.723000000000001</v>
+        <v>8.881600000000001</v>
       </c>
       <c r="G57">
         <v>1.4</v>
@@ -6092,45 +6092,45 @@
         <v>2.02</v>
       </c>
       <c r="M57">
-        <v>0.5041894000000001</v>
+        <v>0.5444420800000001</v>
       </c>
       <c r="N57">
-        <v>1.5158106</v>
+        <v>1.47555792</v>
       </c>
       <c r="O57">
-        <v>0.30316212</v>
+        <v>0.295111584</v>
       </c>
       <c r="P57">
-        <v>1.21264848</v>
+        <v>1.180446336</v>
       </c>
       <c r="Q57">
-        <v>1.38264848</v>
+        <v>1.350446336</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1631408109534422</v>
+        <v>0.1655379674591305</v>
       </c>
       <c r="T57">
-        <v>1.405712679374171</v>
+        <v>1.434429996623899</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.006430916635692</v>
+        <v>3.710220194588926</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1002991056820174</v>
+        <v>0.1002128464349858</v>
       </c>
       <c r="C58">
-        <v>7.893371721782108</v>
+        <v>7.748213111498044</v>
       </c>
       <c r="D58">
-        <v>15.37497172178211</v>
+        <v>15.38841311149804</v>
       </c>
       <c r="E58">
-        <v>6.7216</v>
+        <v>6.8802</v>
       </c>
       <c r="F58">
-        <v>8.881600000000001</v>
+        <v>9.0402</v>
       </c>
       <c r="G58">
         <v>1.4</v>
@@ -6174,28 +6174,28 @@
         <v>2.02</v>
       </c>
       <c r="M58">
-        <v>0.5444420800000001</v>
+        <v>0.5541642600000001</v>
       </c>
       <c r="N58">
-        <v>1.47555792</v>
+        <v>1.46583574</v>
       </c>
       <c r="O58">
-        <v>0.295111584</v>
+        <v>0.293167148</v>
       </c>
       <c r="P58">
-        <v>1.180446336</v>
+        <v>1.172668592</v>
       </c>
       <c r="Q58">
-        <v>1.350446336</v>
+        <v>1.342668592</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1655379674591305</v>
+        <v>0.1680466196162462</v>
       </c>
       <c r="T58">
-        <v>1.434429996623899</v>
+        <v>1.464483003048033</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.710220194588926</v>
+        <v>3.645128612227717</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1002128464349858</v>
+        <v>0.1001265871879543</v>
       </c>
       <c r="C59">
-        <v>7.748213111498044</v>
+        <v>7.603078023734666</v>
       </c>
       <c r="D59">
-        <v>15.38841311149804</v>
+        <v>15.40187802373467</v>
       </c>
       <c r="E59">
-        <v>6.8802</v>
+        <v>7.0388</v>
       </c>
       <c r="F59">
-        <v>9.0402</v>
+        <v>9.1988</v>
       </c>
       <c r="G59">
         <v>1.4</v>
@@ -6256,28 +6256,28 @@
         <v>2.02</v>
       </c>
       <c r="M59">
-        <v>0.5541642600000001</v>
+        <v>0.56388644</v>
       </c>
       <c r="N59">
-        <v>1.46583574</v>
+        <v>1.45611356</v>
       </c>
       <c r="O59">
-        <v>0.293167148</v>
+        <v>0.291222712</v>
       </c>
       <c r="P59">
-        <v>1.172668592</v>
+        <v>1.164890848</v>
       </c>
       <c r="Q59">
-        <v>1.342668592</v>
+        <v>1.334890848</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1680466196162462</v>
+        <v>0.1706747313998911</v>
       </c>
       <c r="T59">
-        <v>1.464483003048033</v>
+        <v>1.495967105016173</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.645128612227717</v>
+        <v>3.582281567189308</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1001265871879543</v>
+        <v>0.1000403279409227</v>
       </c>
       <c r="C60">
-        <v>7.603078023734664</v>
+        <v>7.457966520292892</v>
       </c>
       <c r="D60">
-        <v>15.40187802373466</v>
+        <v>15.41536652029289</v>
       </c>
       <c r="E60">
-        <v>7.038799999999998</v>
+        <v>7.197399999999998</v>
       </c>
       <c r="F60">
-        <v>9.198799999999999</v>
+        <v>9.357399999999998</v>
       </c>
       <c r="G60">
         <v>1.4</v>
@@ -6338,28 +6338,28 @@
         <v>2.02</v>
       </c>
       <c r="M60">
-        <v>0.5638864399999999</v>
+        <v>0.5736086199999999</v>
       </c>
       <c r="N60">
-        <v>1.45611356</v>
+        <v>1.44639138</v>
       </c>
       <c r="O60">
-        <v>0.2912227120000001</v>
+        <v>0.2892782760000001</v>
       </c>
       <c r="P60">
-        <v>1.164890848</v>
+        <v>1.157113104</v>
       </c>
       <c r="Q60">
-        <v>1.334890848</v>
+        <v>1.327113104</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1706747313998911</v>
+        <v>0.1734310437583481</v>
       </c>
       <c r="T60">
-        <v>1.495967105016172</v>
+        <v>1.528987016836417</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.582281567189309</v>
+        <v>3.521564930457287</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1000403279409227</v>
+        <v>0.1012980686938912</v>
       </c>
       <c r="C61">
-        <v>7.457966520292892</v>
+        <v>7.105001298149849</v>
       </c>
       <c r="D61">
-        <v>15.41536652029289</v>
+        <v>15.22100129814985</v>
       </c>
       <c r="E61">
-        <v>7.197399999999998</v>
+        <v>7.356</v>
       </c>
       <c r="F61">
-        <v>9.357399999999998</v>
+        <v>9.516</v>
       </c>
       <c r="G61">
         <v>1.4</v>
@@ -6420,45 +6420,45 @@
         <v>2.02</v>
       </c>
       <c r="M61">
-        <v>0.5736086199999999</v>
+        <v>0.6099756000000001</v>
       </c>
       <c r="N61">
-        <v>1.44639138</v>
+        <v>1.4100244</v>
       </c>
       <c r="O61">
-        <v>0.2892782760000001</v>
+        <v>0.28200488</v>
       </c>
       <c r="P61">
-        <v>1.157113104</v>
+        <v>1.12801952</v>
       </c>
       <c r="Q61">
-        <v>1.327113104</v>
+        <v>1.29801952</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1734310437583481</v>
+        <v>0.1763251717347279</v>
       </c>
       <c r="T61">
-        <v>1.528987016836417</v>
+        <v>1.563657924247674</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.521564930457287</v>
+        <v>3.311607874151032</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1012980686938912</v>
+        <v>0.1012342094468596</v>
       </c>
       <c r="C62">
-        <v>7.105001298149849</v>
+        <v>6.956151614349873</v>
       </c>
       <c r="D62">
-        <v>15.22100129814985</v>
+        <v>15.23075161434987</v>
       </c>
       <c r="E62">
-        <v>7.356</v>
+        <v>7.5146</v>
       </c>
       <c r="F62">
-        <v>9.516</v>
+        <v>9.6746</v>
       </c>
       <c r="G62">
         <v>1.4</v>
@@ -6502,28 +6502,28 @@
         <v>2.02</v>
       </c>
       <c r="M62">
-        <v>0.6099756000000001</v>
+        <v>0.62014186</v>
       </c>
       <c r="N62">
-        <v>1.4100244</v>
+        <v>1.39985814</v>
       </c>
       <c r="O62">
-        <v>0.28200488</v>
+        <v>0.279971628</v>
       </c>
       <c r="P62">
-        <v>1.12801952</v>
+        <v>1.119886512</v>
       </c>
       <c r="Q62">
-        <v>1.29801952</v>
+        <v>1.289886512</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1763251717347279</v>
+        <v>0.1793677165304091</v>
       </c>
       <c r="T62">
-        <v>1.563657924247674</v>
+        <v>1.60010682691079</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.311607874151032</v>
+        <v>3.257319220476425</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1012342094468596</v>
+        <v>0.101170350199828</v>
       </c>
       <c r="C63">
-        <v>6.956151614349873</v>
+        <v>6.807314430332605</v>
       </c>
       <c r="D63">
-        <v>15.23075161434987</v>
+        <v>15.24051443033261</v>
       </c>
       <c r="E63">
-        <v>7.5146</v>
+        <v>7.6732</v>
       </c>
       <c r="F63">
-        <v>9.6746</v>
+        <v>9.8332</v>
       </c>
       <c r="G63">
         <v>1.4</v>
@@ -6584,28 +6584,28 @@
         <v>2.02</v>
       </c>
       <c r="M63">
-        <v>0.62014186</v>
+        <v>0.63030812</v>
       </c>
       <c r="N63">
-        <v>1.39985814</v>
+        <v>1.38969188</v>
       </c>
       <c r="O63">
-        <v>0.279971628</v>
+        <v>0.277938376</v>
       </c>
       <c r="P63">
-        <v>1.119886512</v>
+        <v>1.111753504</v>
       </c>
       <c r="Q63">
-        <v>1.289886512</v>
+        <v>1.281753504</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1793677165304091</v>
+        <v>0.1825703952627052</v>
       </c>
       <c r="T63">
-        <v>1.60010682691079</v>
+        <v>1.638474092871964</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.257319220476425</v>
+        <v>3.204781813694547</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.101170350199828</v>
+        <v>0.1011064909527964</v>
       </c>
       <c r="C64">
-        <v>6.807314430332605</v>
+        <v>6.658489770150306</v>
       </c>
       <c r="D64">
-        <v>15.24051443033261</v>
+        <v>15.25028977015031</v>
       </c>
       <c r="E64">
-        <v>7.6732</v>
+        <v>7.831799999999999</v>
       </c>
       <c r="F64">
-        <v>9.8332</v>
+        <v>9.9918</v>
       </c>
       <c r="G64">
         <v>1.4</v>
@@ -6666,28 +6666,28 @@
         <v>2.02</v>
       </c>
       <c r="M64">
-        <v>0.63030812</v>
+        <v>0.64047438</v>
       </c>
       <c r="N64">
-        <v>1.38969188</v>
+        <v>1.37952562</v>
       </c>
       <c r="O64">
-        <v>0.277938376</v>
+        <v>0.275905124</v>
       </c>
       <c r="P64">
-        <v>1.111753504</v>
+        <v>1.103620496</v>
       </c>
       <c r="Q64">
-        <v>1.281753504</v>
+        <v>1.273620496</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1825703952627052</v>
+        <v>0.1859461917643147</v>
       </c>
       <c r="T64">
-        <v>1.638474092871964</v>
+        <v>1.678915265101311</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.204781813694547</v>
+        <v>3.15391226109622</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1011064909527964</v>
+        <v>0.1010426317057649</v>
       </c>
       <c r="C65">
-        <v>6.658489770150306</v>
+        <v>6.509677657917001</v>
       </c>
       <c r="D65">
-        <v>15.25028977015031</v>
+        <v>15.260077657917</v>
       </c>
       <c r="E65">
-        <v>7.831799999999999</v>
+        <v>7.990399999999999</v>
       </c>
       <c r="F65">
-        <v>9.9918</v>
+        <v>10.1504</v>
       </c>
       <c r="G65">
         <v>1.4</v>
@@ -6748,28 +6748,28 @@
         <v>2.02</v>
       </c>
       <c r="M65">
-        <v>0.64047438</v>
+        <v>0.65064064</v>
       </c>
       <c r="N65">
-        <v>1.37952562</v>
+        <v>1.36935936</v>
       </c>
       <c r="O65">
-        <v>0.275905124</v>
+        <v>0.273871872</v>
       </c>
       <c r="P65">
-        <v>1.103620496</v>
+        <v>1.095487488</v>
       </c>
       <c r="Q65">
-        <v>1.273620496</v>
+        <v>1.265487488</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1859461917643147</v>
+        <v>0.1895095325160135</v>
       </c>
       <c r="T65">
-        <v>1.678915265101311</v>
+        <v>1.721603169121176</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.15391226109622</v>
+        <v>3.104632382016592</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1010426317057649</v>
+        <v>0.1009787724587333</v>
       </c>
       <c r="C66">
-        <v>6.509677657917001</v>
+        <v>6.36087811780863</v>
       </c>
       <c r="D66">
-        <v>15.260077657917</v>
+        <v>15.26987811780863</v>
       </c>
       <c r="E66">
-        <v>7.990399999999999</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="F66">
-        <v>10.1504</v>
+        <v>10.309</v>
       </c>
       <c r="G66">
         <v>1.4</v>
@@ -6830,28 +6830,28 @@
         <v>2.02</v>
       </c>
       <c r="M66">
-        <v>0.65064064</v>
+        <v>0.6608069</v>
       </c>
       <c r="N66">
-        <v>1.36935936</v>
+        <v>1.3591931</v>
       </c>
       <c r="O66">
-        <v>0.273871872</v>
+        <v>0.27183862</v>
       </c>
       <c r="P66">
-        <v>1.095487488</v>
+        <v>1.08735448</v>
       </c>
       <c r="Q66">
-        <v>1.265487488</v>
+        <v>1.25735448</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1895095325160135</v>
+        <v>0.1932764927392379</v>
       </c>
       <c r="T66">
-        <v>1.721603169121176</v>
+        <v>1.766730381942177</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.104632382016592</v>
+        <v>3.056868806908645</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1009787724587333</v>
+        <v>0.1009149132117017</v>
       </c>
       <c r="C67">
-        <v>6.36087811780863</v>
+        <v>6.212091174063307</v>
       </c>
       <c r="D67">
-        <v>15.26987811780863</v>
+        <v>15.27969117406331</v>
       </c>
       <c r="E67">
-        <v>8.148999999999999</v>
+        <v>8.307600000000001</v>
       </c>
       <c r="F67">
-        <v>10.309</v>
+        <v>10.4676</v>
       </c>
       <c r="G67">
         <v>1.4</v>
@@ -6912,28 +6912,28 @@
         <v>2.02</v>
       </c>
       <c r="M67">
-        <v>0.6608069</v>
+        <v>0.6709731600000001</v>
       </c>
       <c r="N67">
-        <v>1.3591931</v>
+        <v>1.34902684</v>
       </c>
       <c r="O67">
-        <v>0.27183862</v>
+        <v>0.269805368</v>
       </c>
       <c r="P67">
-        <v>1.08735448</v>
+        <v>1.079221472</v>
       </c>
       <c r="Q67">
-        <v>1.25735448</v>
+        <v>1.249221472</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1932764927392379</v>
+        <v>0.1972650388579462</v>
       </c>
       <c r="T67">
-        <v>1.766730381942177</v>
+        <v>1.814512136693825</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.056868806908645</v>
+        <v>3.010552612864574</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1009149132117017</v>
+        <v>0.1050318539646702</v>
       </c>
       <c r="C68">
-        <v>6.212091174063307</v>
+        <v>5.445630775112509</v>
       </c>
       <c r="D68">
-        <v>15.27969117406331</v>
+        <v>14.67183077511251</v>
       </c>
       <c r="E68">
-        <v>8.307600000000001</v>
+        <v>8.466200000000001</v>
       </c>
       <c r="F68">
-        <v>10.4676</v>
+        <v>10.6262</v>
       </c>
       <c r="G68">
         <v>1.4</v>
@@ -6994,45 +6994,45 @@
         <v>2.02</v>
       </c>
       <c r="M68">
-        <v>0.6709731600000001</v>
+        <v>0.7640237800000002</v>
       </c>
       <c r="N68">
-        <v>1.34902684</v>
+        <v>1.25597622</v>
       </c>
       <c r="O68">
-        <v>0.269805368</v>
+        <v>0.251195244</v>
       </c>
       <c r="P68">
-        <v>1.079221472</v>
+        <v>1.004780976</v>
       </c>
       <c r="Q68">
-        <v>1.249221472</v>
+        <v>1.174780976</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1972650388579462</v>
+        <v>0.201495315044455</v>
       </c>
       <c r="T68">
-        <v>1.814512136693825</v>
+        <v>1.865189755369815</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.2</v>
       </c>
       <c r="W68">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.010552612864574</v>
+        <v>2.643896764574526</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1050318539646702</v>
+        <v>0.1050303947176386</v>
       </c>
       <c r="C69">
-        <v>5.445630775112509</v>
+        <v>5.287237662449161</v>
       </c>
       <c r="D69">
-        <v>14.67183077511251</v>
+        <v>14.67203766244916</v>
       </c>
       <c r="E69">
-        <v>8.466200000000001</v>
+        <v>8.6248</v>
       </c>
       <c r="F69">
-        <v>10.6262</v>
+        <v>10.7848</v>
       </c>
       <c r="G69">
         <v>1.4</v>
@@ -7076,28 +7076,28 @@
         <v>2.02</v>
       </c>
       <c r="M69">
-        <v>0.7640237800000002</v>
+        <v>0.7754271200000001</v>
       </c>
       <c r="N69">
-        <v>1.25597622</v>
+        <v>1.24457288</v>
       </c>
       <c r="O69">
-        <v>0.251195244</v>
+        <v>0.248914576</v>
       </c>
       <c r="P69">
-        <v>1.004780976</v>
+        <v>0.9956583039999998</v>
       </c>
       <c r="Q69">
-        <v>1.174780976</v>
+        <v>1.165658304</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.201495315044455</v>
+        <v>0.2059899834926205</v>
       </c>
       <c r="T69">
-        <v>1.865189755369815</v>
+        <v>1.919034725213054</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.643896764574526</v>
+        <v>2.605015929801371</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1050303947176386</v>
+        <v>0.105028935470607</v>
       </c>
       <c r="C70">
-        <v>5.287237662449161</v>
+        <v>5.128844555620521</v>
       </c>
       <c r="D70">
-        <v>14.67203766244916</v>
+        <v>14.67224455562052</v>
       </c>
       <c r="E70">
-        <v>8.6248</v>
+        <v>8.7834</v>
       </c>
       <c r="F70">
-        <v>10.7848</v>
+        <v>10.9434</v>
       </c>
       <c r="G70">
         <v>1.4</v>
@@ -7158,28 +7158,28 @@
         <v>2.02</v>
       </c>
       <c r="M70">
-        <v>0.7754271200000001</v>
+        <v>0.7868304600000001</v>
       </c>
       <c r="N70">
-        <v>1.24457288</v>
+        <v>1.23316954</v>
       </c>
       <c r="O70">
-        <v>0.248914576</v>
+        <v>0.246633908</v>
       </c>
       <c r="P70">
-        <v>0.9956583039999998</v>
+        <v>0.9865356320000001</v>
       </c>
       <c r="Q70">
-        <v>1.165658304</v>
+        <v>1.156535632</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2059899834926205</v>
+        <v>0.2107746305503452</v>
       </c>
       <c r="T70">
-        <v>1.919034725213054</v>
+        <v>1.976353564078438</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.605015929801371</v>
+        <v>2.567262075746279</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.105028935470607</v>
+        <v>0.1050274762235754</v>
       </c>
       <c r="C71">
-        <v>5.128844555620521</v>
+        <v>4.970451454626847</v>
       </c>
       <c r="D71">
-        <v>14.67224455562052</v>
+        <v>14.67245145462685</v>
       </c>
       <c r="E71">
-        <v>8.7834</v>
+        <v>8.942</v>
       </c>
       <c r="F71">
-        <v>10.9434</v>
+        <v>11.102</v>
       </c>
       <c r="G71">
         <v>1.4</v>
@@ -7240,28 +7240,28 @@
         <v>2.02</v>
       </c>
       <c r="M71">
-        <v>0.7868304600000001</v>
+        <v>0.7982338000000001</v>
       </c>
       <c r="N71">
-        <v>1.23316954</v>
+        <v>1.2217662</v>
       </c>
       <c r="O71">
-        <v>0.246633908</v>
+        <v>0.24435324</v>
       </c>
       <c r="P71">
-        <v>0.9865356320000001</v>
+        <v>0.9774129599999999</v>
       </c>
       <c r="Q71">
-        <v>1.156535632</v>
+        <v>1.14741296</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2107746305503452</v>
+        <v>0.2158782540785848</v>
       </c>
       <c r="T71">
-        <v>1.976353564078438</v>
+        <v>2.037493658868181</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.567262075746279</v>
+        <v>2.530586903235618</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1050274762235754</v>
+        <v>0.1072412169765439</v>
       </c>
       <c r="C72">
-        <v>4.970451454626847</v>
+        <v>4.504546301635703</v>
       </c>
       <c r="D72">
-        <v>14.67245145462685</v>
+        <v>14.3651463016357</v>
       </c>
       <c r="E72">
-        <v>8.942</v>
+        <v>9.1006</v>
       </c>
       <c r="F72">
-        <v>11.102</v>
+        <v>11.2606</v>
       </c>
       <c r="G72">
         <v>1.4</v>
@@ -7322,45 +7322,45 @@
         <v>2.02</v>
       </c>
       <c r="M72">
-        <v>0.7982338000000001</v>
+        <v>0.8535534800000001</v>
       </c>
       <c r="N72">
-        <v>1.2217662</v>
+        <v>1.16644652</v>
       </c>
       <c r="O72">
-        <v>0.24435324</v>
+        <v>0.233289304</v>
       </c>
       <c r="P72">
-        <v>0.9774129599999999</v>
+        <v>0.933157216</v>
       </c>
       <c r="Q72">
-        <v>1.14741296</v>
+        <v>1.103157216</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2158782540785848</v>
+        <v>0.2213338516432548</v>
       </c>
       <c r="T72">
-        <v>2.037493658868181</v>
+        <v>2.102850311919286</v>
       </c>
       <c r="U72">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.2</v>
       </c>
       <c r="W72">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.530586903235618</v>
+        <v>2.366576960122053</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1072412169765439</v>
+        <v>0.1072709577295123</v>
       </c>
       <c r="C73">
-        <v>4.504546301635704</v>
+        <v>4.341905381845336</v>
       </c>
       <c r="D73">
-        <v>14.3651463016357</v>
+        <v>14.36110538184534</v>
       </c>
       <c r="E73">
-        <v>9.100599999999998</v>
+        <v>9.2592</v>
       </c>
       <c r="F73">
-        <v>11.2606</v>
+        <v>11.4192</v>
       </c>
       <c r="G73">
         <v>1.4</v>
@@ -7404,28 +7404,28 @@
         <v>2.02</v>
       </c>
       <c r="M73">
-        <v>0.85355348</v>
+        <v>0.8655753600000001</v>
       </c>
       <c r="N73">
-        <v>1.16644652</v>
+        <v>1.15442464</v>
       </c>
       <c r="O73">
-        <v>0.233289304</v>
+        <v>0.230884928</v>
       </c>
       <c r="P73">
-        <v>0.933157216</v>
+        <v>0.9235397119999998</v>
       </c>
       <c r="Q73">
-        <v>1.103157216</v>
+        <v>1.093539712</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2213338516432547</v>
+        <v>0.2271791347482582</v>
       </c>
       <c r="T73">
-        <v>2.102850311919285</v>
+        <v>2.172875297331183</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.366576960122054</v>
+        <v>2.333707835675913</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1072709577295123</v>
+        <v>0.1073006984824807</v>
       </c>
       <c r="C74">
-        <v>4.341905381845336</v>
+        <v>4.179266734839432</v>
       </c>
       <c r="D74">
-        <v>14.36110538184534</v>
+        <v>14.35706673483943</v>
       </c>
       <c r="E74">
-        <v>9.2592</v>
+        <v>9.4178</v>
       </c>
       <c r="F74">
-        <v>11.4192</v>
+        <v>11.5778</v>
       </c>
       <c r="G74">
         <v>1.4</v>
@@ -7486,28 +7486,28 @@
         <v>2.02</v>
       </c>
       <c r="M74">
-        <v>0.8655753600000001</v>
+        <v>0.8775972400000001</v>
       </c>
       <c r="N74">
-        <v>1.15442464</v>
+        <v>1.14240276</v>
       </c>
       <c r="O74">
-        <v>0.230884928</v>
+        <v>0.228480552</v>
       </c>
       <c r="P74">
-        <v>0.9235397119999998</v>
+        <v>0.913922208</v>
       </c>
       <c r="Q74">
-        <v>1.093539712</v>
+        <v>1.083922208</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2271791347482582</v>
+        <v>0.2334574017869656</v>
       </c>
       <c r="T74">
-        <v>2.172875297331183</v>
+        <v>2.248087318699517</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.333707835675913</v>
+        <v>2.301739235187203</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1073006984824807</v>
+        <v>0.1073304392354491</v>
       </c>
       <c r="C75">
-        <v>4.179266734839432</v>
+        <v>4.016630358701072</v>
       </c>
       <c r="D75">
-        <v>14.35706673483943</v>
+        <v>14.35303035870107</v>
       </c>
       <c r="E75">
-        <v>9.4178</v>
+        <v>9.5764</v>
       </c>
       <c r="F75">
-        <v>11.5778</v>
+        <v>11.7364</v>
       </c>
       <c r="G75">
         <v>1.4</v>
@@ -7568,28 +7568,28 @@
         <v>2.02</v>
       </c>
       <c r="M75">
-        <v>0.8775972400000001</v>
+        <v>0.8896191200000001</v>
       </c>
       <c r="N75">
-        <v>1.14240276</v>
+        <v>1.13038088</v>
       </c>
       <c r="O75">
-        <v>0.228480552</v>
+        <v>0.226076176</v>
       </c>
       <c r="P75">
-        <v>0.913922208</v>
+        <v>0.904304704</v>
       </c>
       <c r="Q75">
-        <v>1.083922208</v>
+        <v>1.074304704</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2334574017869656</v>
+        <v>0.2402186124440351</v>
       </c>
       <c r="T75">
-        <v>2.248087318699517</v>
+        <v>2.329084880173108</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.301739235187203</v>
+        <v>2.270634650927916</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1073304392354491</v>
+        <v>0.1073601799884176</v>
       </c>
       <c r="C76">
-        <v>4.016630358701072</v>
+        <v>3.853996251515476</v>
       </c>
       <c r="D76">
-        <v>14.35303035870107</v>
+        <v>14.34899625151547</v>
       </c>
       <c r="E76">
-        <v>9.5764</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="F76">
-        <v>11.7364</v>
+        <v>11.895</v>
       </c>
       <c r="G76">
         <v>1.4</v>
@@ -7650,28 +7650,28 @@
         <v>2.02</v>
       </c>
       <c r="M76">
-        <v>0.8896191200000001</v>
+        <v>0.901641</v>
       </c>
       <c r="N76">
-        <v>1.13038088</v>
+        <v>1.118359</v>
       </c>
       <c r="O76">
-        <v>0.226076176</v>
+        <v>0.2236718</v>
       </c>
       <c r="P76">
-        <v>0.904304704</v>
+        <v>0.8946871999999999</v>
       </c>
       <c r="Q76">
-        <v>1.074304704</v>
+        <v>1.0646872</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2402186124440351</v>
+        <v>0.2475207199536703</v>
       </c>
       <c r="T76">
-        <v>2.329084880173108</v>
+        <v>2.416562246564587</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.270634650927916</v>
+        <v>2.240359522248877</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1073601799884176</v>
+        <v>0.107389920741386</v>
       </c>
       <c r="C77">
-        <v>3.853996251515476</v>
+        <v>3.69136441137003</v>
       </c>
       <c r="D77">
-        <v>14.34899625151547</v>
+        <v>14.34496441137003</v>
       </c>
       <c r="E77">
-        <v>9.734999999999999</v>
+        <v>9.893599999999999</v>
       </c>
       <c r="F77">
-        <v>11.895</v>
+        <v>12.0536</v>
       </c>
       <c r="G77">
         <v>1.4</v>
@@ -7732,28 +7732,28 @@
         <v>2.02</v>
       </c>
       <c r="M77">
-        <v>0.901641</v>
+        <v>0.9136628800000001</v>
       </c>
       <c r="N77">
-        <v>1.118359</v>
+        <v>1.10633712</v>
       </c>
       <c r="O77">
-        <v>0.2236718</v>
+        <v>0.221267424</v>
       </c>
       <c r="P77">
-        <v>0.8946871999999999</v>
+        <v>0.8850696960000001</v>
       </c>
       <c r="Q77">
-        <v>1.0646872</v>
+        <v>1.055069696</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2475207199536703</v>
+        <v>0.2554313364224417</v>
       </c>
       <c r="T77">
-        <v>2.416562246564587</v>
+        <v>2.511329393488688</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.240359522248877</v>
+        <v>2.210881107482445</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.107389920741386</v>
+        <v>0.1074196614943544</v>
       </c>
       <c r="C78">
-        <v>3.69136441137003</v>
+        <v>3.528734836354264</v>
       </c>
       <c r="D78">
-        <v>14.34496441137003</v>
+        <v>14.34093483635426</v>
       </c>
       <c r="E78">
-        <v>9.893599999999999</v>
+        <v>10.0522</v>
       </c>
       <c r="F78">
-        <v>12.0536</v>
+        <v>12.2122</v>
       </c>
       <c r="G78">
         <v>1.4</v>
@@ -7814,28 +7814,28 @@
         <v>2.02</v>
       </c>
       <c r="M78">
-        <v>0.9136628800000001</v>
+        <v>0.92568476</v>
       </c>
       <c r="N78">
-        <v>1.10633712</v>
+        <v>1.09431524</v>
       </c>
       <c r="O78">
-        <v>0.221267424</v>
+        <v>0.218863048</v>
       </c>
       <c r="P78">
-        <v>0.8850696960000001</v>
+        <v>0.875452192</v>
       </c>
       <c r="Q78">
-        <v>1.055069696</v>
+        <v>1.045452192</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2554313364224417</v>
+        <v>0.2640298325841497</v>
       </c>
       <c r="T78">
-        <v>2.511329393488688</v>
+        <v>2.614337161884451</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.210881107482445</v>
+        <v>2.182168365826828</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1074196614943544</v>
+        <v>0.1074494022473229</v>
       </c>
       <c r="C79">
-        <v>3.528734836354264</v>
+        <v>3.366107524559855</v>
       </c>
       <c r="D79">
-        <v>14.34093483635426</v>
+        <v>14.33690752455985</v>
       </c>
       <c r="E79">
-        <v>10.0522</v>
+        <v>10.2108</v>
       </c>
       <c r="F79">
-        <v>12.2122</v>
+        <v>12.3708</v>
       </c>
       <c r="G79">
         <v>1.4</v>
@@ -7896,28 +7896,28 @@
         <v>2.02</v>
       </c>
       <c r="M79">
-        <v>0.92568476</v>
+        <v>0.93770664</v>
       </c>
       <c r="N79">
-        <v>1.09431524</v>
+        <v>1.08229336</v>
       </c>
       <c r="O79">
-        <v>0.218863048</v>
+        <v>0.216458672</v>
       </c>
       <c r="P79">
-        <v>0.875452192</v>
+        <v>0.865834688</v>
       </c>
       <c r="Q79">
-        <v>1.045452192</v>
+        <v>1.035834688</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2640298325841497</v>
+        <v>0.2734100102151039</v>
       </c>
       <c r="T79">
-        <v>2.614337161884451</v>
+        <v>2.726709272861646</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.182168365826828</v>
+        <v>2.154191848316228</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1074494022473229</v>
+        <v>0.1074791430002913</v>
       </c>
       <c r="C80">
-        <v>3.366107524559855</v>
+        <v>3.203482474080614</v>
       </c>
       <c r="D80">
-        <v>14.33690752455985</v>
+        <v>14.33288247408061</v>
       </c>
       <c r="E80">
-        <v>10.2108</v>
+        <v>10.3694</v>
       </c>
       <c r="F80">
-        <v>12.3708</v>
+        <v>12.5294</v>
       </c>
       <c r="G80">
         <v>1.4</v>
@@ -7978,28 +7978,28 @@
         <v>2.02</v>
       </c>
       <c r="M80">
-        <v>0.93770664</v>
+        <v>0.9497285200000002</v>
       </c>
       <c r="N80">
-        <v>1.08229336</v>
+        <v>1.07027148</v>
       </c>
       <c r="O80">
-        <v>0.216458672</v>
+        <v>0.2140542959999999</v>
       </c>
       <c r="P80">
-        <v>0.865834688</v>
+        <v>0.8562171839999998</v>
       </c>
       <c r="Q80">
-        <v>1.035834688</v>
+        <v>1.026217184</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2734100102151039</v>
+        <v>0.2836835380966252</v>
       </c>
       <c r="T80">
-        <v>2.726709272861646</v>
+        <v>2.849783489646194</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.154191848316228</v>
+        <v>2.126923597071718</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1074791430002913</v>
+        <v>0.1075088837532597</v>
       </c>
       <c r="C81">
-        <v>3.203482474080614</v>
+        <v>3.04085968301251</v>
       </c>
       <c r="D81">
-        <v>14.33288247408061</v>
+        <v>14.32885968301251</v>
       </c>
       <c r="E81">
-        <v>10.3694</v>
+        <v>10.528</v>
       </c>
       <c r="F81">
-        <v>12.5294</v>
+        <v>12.688</v>
       </c>
       <c r="G81">
         <v>1.4</v>
@@ -8060,28 +8060,28 @@
         <v>2.02</v>
       </c>
       <c r="M81">
-        <v>0.9497285200000002</v>
+        <v>0.9617504000000001</v>
       </c>
       <c r="N81">
-        <v>1.07027148</v>
+        <v>1.0582496</v>
       </c>
       <c r="O81">
-        <v>0.2140542959999999</v>
+        <v>0.21164992</v>
       </c>
       <c r="P81">
-        <v>0.8562171839999998</v>
+        <v>0.84659968</v>
       </c>
       <c r="Q81">
-        <v>1.026217184</v>
+        <v>1.01659968</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2836835380966252</v>
+        <v>0.2949844187662987</v>
       </c>
       <c r="T81">
-        <v>2.849783489646194</v>
+        <v>2.985165128109196</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.126923597071718</v>
+        <v>2.100337052108322</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1075088837532597</v>
+        <v>0.1075386245062282</v>
       </c>
       <c r="C82">
-        <v>3.04085968301251</v>
+        <v>2.878239149453634</v>
       </c>
       <c r="D82">
-        <v>14.32885968301251</v>
+        <v>14.32483914945363</v>
       </c>
       <c r="E82">
-        <v>10.528</v>
+        <v>10.6866</v>
       </c>
       <c r="F82">
-        <v>12.688</v>
+        <v>12.8466</v>
       </c>
       <c r="G82">
         <v>1.4</v>
@@ -8142,28 +8142,28 @@
         <v>2.02</v>
       </c>
       <c r="M82">
-        <v>0.9617504000000001</v>
+        <v>0.9737722800000002</v>
       </c>
       <c r="N82">
-        <v>1.0582496</v>
+        <v>1.04622772</v>
       </c>
       <c r="O82">
-        <v>0.21164992</v>
+        <v>0.209245544</v>
       </c>
       <c r="P82">
-        <v>0.84659968</v>
+        <v>0.8369821759999999</v>
       </c>
       <c r="Q82">
-        <v>1.01659968</v>
+        <v>1.006982176</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2949844187662987</v>
+        <v>0.3074748658222535</v>
       </c>
       <c r="T82">
-        <v>2.985165128109196</v>
+        <v>3.134797465357777</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.100337052108322</v>
+        <v>2.074406965045257</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1075386245062282</v>
+        <v>0.1075683652591966</v>
       </c>
       <c r="C83">
-        <v>2.878239149453634</v>
+        <v>2.715620871504223</v>
       </c>
       <c r="D83">
-        <v>14.32483914945363</v>
+        <v>14.32082087150422</v>
       </c>
       <c r="E83">
-        <v>10.6866</v>
+        <v>10.8452</v>
       </c>
       <c r="F83">
-        <v>12.8466</v>
+        <v>13.0052</v>
       </c>
       <c r="G83">
         <v>1.4</v>
@@ -8224,28 +8224,28 @@
         <v>2.02</v>
       </c>
       <c r="M83">
-        <v>0.9737722800000002</v>
+        <v>0.9857941600000001</v>
       </c>
       <c r="N83">
-        <v>1.04622772</v>
+        <v>1.03420584</v>
       </c>
       <c r="O83">
-        <v>0.209245544</v>
+        <v>0.206841168</v>
       </c>
       <c r="P83">
-        <v>0.8369821759999999</v>
+        <v>0.8273646719999999</v>
       </c>
       <c r="Q83">
-        <v>1.006982176</v>
+        <v>0.9973646719999998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3074748658222535</v>
+        <v>0.32135314032887</v>
       </c>
       <c r="T83">
-        <v>3.134797465357777</v>
+        <v>3.301055617856201</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.074406965045257</v>
+        <v>2.04910931913007</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1075683652591966</v>
+        <v>0.107598106012165</v>
       </c>
       <c r="C84">
-        <v>2.715620871504223</v>
+        <v>2.553004847266626</v>
       </c>
       <c r="D84">
-        <v>14.32082087150422</v>
+        <v>14.31680484726663</v>
       </c>
       <c r="E84">
-        <v>10.8452</v>
+        <v>11.0038</v>
       </c>
       <c r="F84">
-        <v>13.0052</v>
+        <v>13.1638</v>
       </c>
       <c r="G84">
         <v>1.4</v>
@@ -8306,28 +8306,28 @@
         <v>2.02</v>
       </c>
       <c r="M84">
-        <v>0.9857941600000001</v>
+        <v>0.9978160400000001</v>
       </c>
       <c r="N84">
-        <v>1.03420584</v>
+        <v>1.02218396</v>
       </c>
       <c r="O84">
-        <v>0.206841168</v>
+        <v>0.204436792</v>
       </c>
       <c r="P84">
-        <v>0.8273646719999999</v>
+        <v>0.817747168</v>
       </c>
       <c r="Q84">
-        <v>0.9973646719999998</v>
+        <v>0.987747168</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.32135314032887</v>
+        <v>0.3368641530127355</v>
       </c>
       <c r="T84">
-        <v>3.301055617856201</v>
+        <v>3.486873553001498</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.04910931913007</v>
+        <v>2.024421255044166</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.107598106012165</v>
+        <v>0.1076278467651335</v>
       </c>
       <c r="C85">
-        <v>2.553004847266626</v>
+        <v>2.39039107484534</v>
       </c>
       <c r="D85">
-        <v>14.31680484726663</v>
+        <v>14.31279107484534</v>
       </c>
       <c r="E85">
-        <v>11.0038</v>
+        <v>11.1624</v>
       </c>
       <c r="F85">
-        <v>13.1638</v>
+        <v>13.3224</v>
       </c>
       <c r="G85">
         <v>1.4</v>
@@ -8388,28 +8388,28 @@
         <v>2.02</v>
       </c>
       <c r="M85">
-        <v>0.9978160400000001</v>
+        <v>1.00983792</v>
       </c>
       <c r="N85">
-        <v>1.02218396</v>
+        <v>1.01016208</v>
       </c>
       <c r="O85">
-        <v>0.204436792</v>
+        <v>0.202032416</v>
       </c>
       <c r="P85">
-        <v>0.817747168</v>
+        <v>0.808129664</v>
       </c>
       <c r="Q85">
-        <v>0.987747168</v>
+        <v>0.9781296639999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3368641530127355</v>
+        <v>0.3543140422820841</v>
       </c>
       <c r="T85">
-        <v>3.486873553001498</v>
+        <v>3.695918730039958</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.024421255044166</v>
+        <v>2.000321002007926</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1076278467651334</v>
+        <v>0.1173135875181019</v>
       </c>
       <c r="C86">
-        <v>2.390391074845343</v>
+        <v>1.034316513196382</v>
       </c>
       <c r="D86">
-        <v>14.31279107484534</v>
+        <v>13.11531651319638</v>
       </c>
       <c r="E86">
-        <v>11.1624</v>
+        <v>11.321</v>
       </c>
       <c r="F86">
-        <v>13.3224</v>
+        <v>13.481</v>
       </c>
       <c r="G86">
         <v>1.4</v>
@@ -8470,45 +8470,45 @@
         <v>2.02</v>
       </c>
       <c r="M86">
-        <v>1.00983792</v>
+        <v>1.21329</v>
       </c>
       <c r="N86">
-        <v>1.01016208</v>
+        <v>0.80671</v>
       </c>
       <c r="O86">
-        <v>0.202032416</v>
+        <v>0.161342</v>
       </c>
       <c r="P86">
-        <v>0.808129664</v>
+        <v>0.6453680000000001</v>
       </c>
       <c r="Q86">
-        <v>0.9781296639999999</v>
+        <v>0.815368</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3543140422820839</v>
+        <v>0.3740905834540124</v>
       </c>
       <c r="T86">
-        <v>3.695918730039955</v>
+        <v>3.932836597350209</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.2</v>
       </c>
       <c r="W86">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.000321002007926</v>
+        <v>1.664894625357499</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1173135875181019</v>
+        <v>0.1174569282710703</v>
       </c>
       <c r="C87">
-        <v>1.034316513196382</v>
+        <v>0.8594976584149183</v>
       </c>
       <c r="D87">
-        <v>13.11531651319638</v>
+        <v>13.09909765841492</v>
       </c>
       <c r="E87">
-        <v>11.321</v>
+        <v>11.4796</v>
       </c>
       <c r="F87">
-        <v>13.481</v>
+        <v>13.6396</v>
       </c>
       <c r="G87">
         <v>1.4</v>
@@ -8552,28 +8552,28 @@
         <v>2.02</v>
       </c>
       <c r="M87">
-        <v>1.21329</v>
+        <v>1.227564</v>
       </c>
       <c r="N87">
-        <v>0.80671</v>
+        <v>0.7924360000000001</v>
       </c>
       <c r="O87">
-        <v>0.161342</v>
+        <v>0.1584872000000001</v>
       </c>
       <c r="P87">
-        <v>0.6453680000000001</v>
+        <v>0.6339488000000001</v>
       </c>
       <c r="Q87">
-        <v>0.815368</v>
+        <v>0.8039488</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3740905834540124</v>
+        <v>0.3966923447933592</v>
       </c>
       <c r="T87">
-        <v>3.932836597350209</v>
+        <v>4.203599874276214</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.664894625357499</v>
+        <v>1.645535385527761</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1174569282710703</v>
+        <v>0.1176002690240387</v>
       </c>
       <c r="C88">
-        <v>0.8594976584149183</v>
+        <v>0.6847188676843139</v>
       </c>
       <c r="D88">
-        <v>13.09909765841492</v>
+        <v>13.08291886768431</v>
       </c>
       <c r="E88">
-        <v>11.4796</v>
+        <v>11.6382</v>
       </c>
       <c r="F88">
-        <v>13.6396</v>
+        <v>13.7982</v>
       </c>
       <c r="G88">
         <v>1.4</v>
@@ -8634,28 +8634,28 @@
         <v>2.02</v>
       </c>
       <c r="M88">
-        <v>1.227564</v>
+        <v>1.241838</v>
       </c>
       <c r="N88">
-        <v>0.7924360000000001</v>
+        <v>0.778162</v>
       </c>
       <c r="O88">
-        <v>0.1584872000000001</v>
+        <v>0.1556324</v>
       </c>
       <c r="P88">
-        <v>0.6339488000000001</v>
+        <v>0.6225296</v>
       </c>
       <c r="Q88">
-        <v>0.8039488</v>
+        <v>0.7925295999999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3966923447933592</v>
+        <v>0.4227713001849133</v>
       </c>
       <c r="T88">
-        <v>4.203599874276214</v>
+        <v>4.516019039960065</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.645535385527761</v>
+        <v>1.626621185694108</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1176002690240387</v>
+        <v>0.1177436097770072</v>
       </c>
       <c r="C89">
-        <v>0.6847188676843139</v>
+        <v>0.5099799927374935</v>
       </c>
       <c r="D89">
-        <v>13.08291886768431</v>
+        <v>13.06677999273749</v>
       </c>
       <c r="E89">
-        <v>11.6382</v>
+        <v>11.7968</v>
       </c>
       <c r="F89">
-        <v>13.7982</v>
+        <v>13.9568</v>
       </c>
       <c r="G89">
         <v>1.4</v>
@@ -8716,28 +8716,28 @@
         <v>2.02</v>
       </c>
       <c r="M89">
-        <v>1.241838</v>
+        <v>1.256112</v>
       </c>
       <c r="N89">
-        <v>0.778162</v>
+        <v>0.7638880000000001</v>
       </c>
       <c r="O89">
-        <v>0.1556324</v>
+        <v>0.1527776</v>
       </c>
       <c r="P89">
-        <v>0.6225296</v>
+        <v>0.6111104000000001</v>
       </c>
       <c r="Q89">
-        <v>0.7925295999999999</v>
+        <v>0.7811104</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4227713001849133</v>
+        <v>0.4531967481417263</v>
       </c>
       <c r="T89">
-        <v>4.516019039960065</v>
+        <v>4.880508066591224</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.626621185694108</v>
+        <v>1.608136854038493</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1177436097770072</v>
+        <v>0.1178869505299756</v>
       </c>
       <c r="C90">
-        <v>0.5099799927374935</v>
+        <v>0.3352808860380794</v>
       </c>
       <c r="D90">
-        <v>13.06677999273749</v>
+        <v>13.05068088603808</v>
       </c>
       <c r="E90">
-        <v>11.7968</v>
+        <v>11.9554</v>
       </c>
       <c r="F90">
-        <v>13.9568</v>
+        <v>14.1154</v>
       </c>
       <c r="G90">
         <v>1.4</v>
@@ -8798,28 +8798,28 @@
         <v>2.02</v>
       </c>
       <c r="M90">
-        <v>1.256112</v>
+        <v>1.270386</v>
       </c>
       <c r="N90">
-        <v>0.7638880000000001</v>
+        <v>0.7496140000000002</v>
       </c>
       <c r="O90">
-        <v>0.1527776</v>
+        <v>0.1499228000000001</v>
       </c>
       <c r="P90">
-        <v>0.6111104000000001</v>
+        <v>0.5996912000000002</v>
       </c>
       <c r="Q90">
-        <v>0.7811104</v>
+        <v>0.7696912000000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4531967481417263</v>
+        <v>0.4891540957270508</v>
       </c>
       <c r="T90">
-        <v>4.880508066591224</v>
+        <v>5.31126782533714</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.608136854038493</v>
+        <v>1.590067900622331</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1178869505299756</v>
+        <v>0.118030291282944</v>
       </c>
       <c r="C91">
-        <v>0.3352808860380794</v>
+        <v>0.1606214007758968</v>
       </c>
       <c r="D91">
-        <v>13.05068088603808</v>
+        <v>13.0346214007759</v>
       </c>
       <c r="E91">
-        <v>11.9554</v>
+        <v>12.114</v>
       </c>
       <c r="F91">
-        <v>14.1154</v>
+        <v>14.274</v>
       </c>
       <c r="G91">
         <v>1.4</v>
@@ -8880,28 +8880,28 @@
         <v>2.02</v>
       </c>
       <c r="M91">
-        <v>1.270386</v>
+        <v>1.28466</v>
       </c>
       <c r="N91">
-        <v>0.7496140000000002</v>
+        <v>0.7353400000000001</v>
       </c>
       <c r="O91">
-        <v>0.1499228000000001</v>
+        <v>0.147068</v>
       </c>
       <c r="P91">
-        <v>0.5996912000000002</v>
+        <v>0.5882720000000001</v>
       </c>
       <c r="Q91">
-        <v>0.7696912000000001</v>
+        <v>0.7582720000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4891540957270508</v>
+        <v>0.5323029128294403</v>
       </c>
       <c r="T91">
-        <v>5.31126782533714</v>
+        <v>5.82817953583224</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.590067900622331</v>
+        <v>1.572400479504305</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.118030291282944</v>
+        <v>0.1181736320359124</v>
       </c>
       <c r="C92">
-        <v>0.1606214007758968</v>
+        <v>-0.01399860913749151</v>
       </c>
       <c r="D92">
-        <v>13.0346214007759</v>
+        <v>13.01860139086251</v>
       </c>
       <c r="E92">
-        <v>12.114</v>
+        <v>12.2726</v>
       </c>
       <c r="F92">
-        <v>14.274</v>
+        <v>14.4326</v>
       </c>
       <c r="G92">
         <v>1.4</v>
@@ -8962,28 +8962,28 @@
         <v>2.02</v>
       </c>
       <c r="M92">
-        <v>1.28466</v>
+        <v>1.298934</v>
       </c>
       <c r="N92">
-        <v>0.7353400000000001</v>
+        <v>0.721066</v>
       </c>
       <c r="O92">
-        <v>0.147068</v>
+        <v>0.1442132</v>
       </c>
       <c r="P92">
-        <v>0.5882720000000001</v>
+        <v>0.5768527999999999</v>
       </c>
       <c r="Q92">
-        <v>0.7582720000000001</v>
+        <v>0.7468527999999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5323029128294403</v>
+        <v>0.5850403559545828</v>
       </c>
       <c r="T92">
-        <v>5.82817953583224</v>
+        <v>6.45996051532625</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.572400479504305</v>
+        <v>1.555121353355906</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1181736320359124</v>
+        <v>0.1183169727888809</v>
       </c>
       <c r="C93">
-        <v>-0.01399860913749151</v>
+        <v>-0.1885792890732123</v>
       </c>
       <c r="D93">
-        <v>13.01860139086251</v>
+        <v>13.00262071092679</v>
       </c>
       <c r="E93">
-        <v>12.2726</v>
+        <v>12.4312</v>
       </c>
       <c r="F93">
-        <v>14.4326</v>
+        <v>14.5912</v>
       </c>
       <c r="G93">
         <v>1.4</v>
@@ -9044,28 +9044,28 @@
         <v>2.02</v>
       </c>
       <c r="M93">
-        <v>1.298934</v>
+        <v>1.313208</v>
       </c>
       <c r="N93">
-        <v>0.721066</v>
+        <v>0.7067920000000001</v>
       </c>
       <c r="O93">
-        <v>0.1442132</v>
+        <v>0.1413584</v>
       </c>
       <c r="P93">
-        <v>0.5768527999999999</v>
+        <v>0.5654336000000001</v>
       </c>
       <c r="Q93">
-        <v>0.7468527999999999</v>
+        <v>0.7354336</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5850403559545828</v>
+        <v>0.6509621598610112</v>
       </c>
       <c r="T93">
-        <v>6.45996051532625</v>
+        <v>7.249686739693765</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.555121353355906</v>
+        <v>1.538217860384646</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1183169727888809</v>
+        <v>0.1184603135418493</v>
       </c>
       <c r="C94">
-        <v>-0.1885792890732123</v>
+        <v>-0.3631207836894763</v>
       </c>
       <c r="D94">
-        <v>13.00262071092679</v>
+        <v>12.98667921631052</v>
       </c>
       <c r="E94">
-        <v>12.4312</v>
+        <v>12.5898</v>
       </c>
       <c r="F94">
-        <v>14.5912</v>
+        <v>14.7498</v>
       </c>
       <c r="G94">
         <v>1.4</v>
@@ -9126,28 +9126,28 @@
         <v>2.02</v>
       </c>
       <c r="M94">
-        <v>1.313208</v>
+        <v>1.327482</v>
       </c>
       <c r="N94">
-        <v>0.7067920000000001</v>
+        <v>0.692518</v>
       </c>
       <c r="O94">
-        <v>0.1413584</v>
+        <v>0.1385036</v>
       </c>
       <c r="P94">
-        <v>0.5654336000000001</v>
+        <v>0.5540144</v>
       </c>
       <c r="Q94">
-        <v>0.7354336</v>
+        <v>0.7240143999999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6509621598610112</v>
+        <v>0.7357187648835619</v>
       </c>
       <c r="T94">
-        <v>7.249686739693765</v>
+        <v>8.265049028166281</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.538217860384646</v>
+        <v>1.521677883391263</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1184603135418493</v>
+        <v>0.1186036542948177</v>
       </c>
       <c r="C95">
-        <v>-0.3631207836894763</v>
+        <v>-0.5376232369359499</v>
       </c>
       <c r="D95">
-        <v>12.98667921631052</v>
+        <v>12.97077676306405</v>
       </c>
       <c r="E95">
-        <v>12.5898</v>
+        <v>12.7484</v>
       </c>
       <c r="F95">
-        <v>14.7498</v>
+        <v>14.9084</v>
       </c>
       <c r="G95">
         <v>1.4</v>
@@ -9208,28 +9208,28 @@
         <v>2.02</v>
       </c>
       <c r="M95">
-        <v>1.327482</v>
+        <v>1.341756</v>
       </c>
       <c r="N95">
-        <v>0.692518</v>
+        <v>0.6782440000000001</v>
       </c>
       <c r="O95">
-        <v>0.1385036</v>
+        <v>0.1356488</v>
       </c>
       <c r="P95">
-        <v>0.5540144</v>
+        <v>0.5425952000000001</v>
       </c>
       <c r="Q95">
-        <v>0.7240143999999999</v>
+        <v>0.7125952</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7357187648835619</v>
+        <v>0.8487275715802962</v>
       </c>
       <c r="T95">
-        <v>8.265049028166281</v>
+        <v>9.618865412796305</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.521677883391263</v>
+        <v>1.505489820801994</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1186036542948177</v>
+        <v>0.1653117981379144</v>
       </c>
       <c r="C96">
-        <v>-0.5376232369359499</v>
+        <v>-4.395634680653124</v>
       </c>
       <c r="D96">
-        <v>12.97077676306405</v>
+        <v>9.271365319346875</v>
       </c>
       <c r="E96">
-        <v>12.7484</v>
+        <v>12.907</v>
       </c>
       <c r="F96">
-        <v>14.9084</v>
+        <v>15.067</v>
       </c>
       <c r="G96">
         <v>1.4</v>
@@ -9290,45 +9290,45 @@
         <v>2.02</v>
       </c>
       <c r="M96">
-        <v>1.341756</v>
+        <v>2.2118356</v>
       </c>
       <c r="N96">
-        <v>0.6782440000000001</v>
+        <v>-0.1918356000000001</v>
       </c>
       <c r="O96">
-        <v>0.1356488</v>
+        <v>-0.03836712000000003</v>
       </c>
       <c r="P96">
-        <v>0.5425952000000001</v>
+        <v>-0.1534684800000001</v>
       </c>
       <c r="Q96">
-        <v>0.7125952</v>
+        <v>0.01653151999999986</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8487275715802962</v>
+        <v>1.026493718117685</v>
       </c>
       <c r="T96">
-        <v>9.618865412796305</v>
+        <v>11.74845804233969</v>
       </c>
       <c r="U96">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2</v>
+        <v>0.182653719833427</v>
       </c>
       <c r="W96">
-        <v>0.07199999999999999</v>
+        <v>0.1199864339284529</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.505489820801994</v>
+        <v>0.9132685991671352</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1653117981379144</v>
+        <v>0.1663217981379145</v>
       </c>
       <c r="C97">
-        <v>-4.395634680653124</v>
+        <v>-4.611063536006256</v>
       </c>
       <c r="D97">
-        <v>9.271365319346875</v>
+        <v>9.214536463993744</v>
       </c>
       <c r="E97">
-        <v>12.907</v>
+        <v>13.0656</v>
       </c>
       <c r="F97">
-        <v>15.067</v>
+        <v>15.2256</v>
       </c>
       <c r="G97">
         <v>1.4</v>
@@ -9372,37 +9372,37 @@
         <v>2.02</v>
       </c>
       <c r="M97">
-        <v>2.2118356</v>
+        <v>2.23511808</v>
       </c>
       <c r="N97">
-        <v>-0.1918356000000001</v>
+        <v>-0.2151180800000003</v>
       </c>
       <c r="O97">
-        <v>-0.03836712000000003</v>
+        <v>-0.04302361600000007</v>
       </c>
       <c r="P97">
-        <v>-0.1534684800000001</v>
+        <v>-0.1720944640000003</v>
       </c>
       <c r="Q97">
-        <v>0.01653151999999986</v>
+        <v>-0.002094464000000323</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.026493718117685</v>
+        <v>1.271667147647106</v>
       </c>
       <c r="T97">
-        <v>11.74845804233969</v>
+        <v>14.68557255292462</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.182653719833427</v>
+        <v>0.1807510769184955</v>
       </c>
       <c r="W97">
-        <v>0.1199864339284529</v>
+        <v>0.1202657419083649</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9132685991671352</v>
+        <v>0.9037553845924774</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1663217981379144</v>
+        <v>0.1673317981379145</v>
       </c>
       <c r="C98">
-        <v>-4.611063536006254</v>
+        <v>-4.825799970352652</v>
       </c>
       <c r="D98">
-        <v>9.214536463993744</v>
+        <v>9.158400029647348</v>
       </c>
       <c r="E98">
-        <v>13.0656</v>
+        <v>13.2242</v>
       </c>
       <c r="F98">
-        <v>15.2256</v>
+        <v>15.3842</v>
       </c>
       <c r="G98">
         <v>1.4</v>
@@ -9454,37 +9454,37 @@
         <v>2.02</v>
       </c>
       <c r="M98">
-        <v>2.23511808</v>
+        <v>2.25840056</v>
       </c>
       <c r="N98">
-        <v>-0.2151180799999999</v>
+        <v>-0.2384005600000001</v>
       </c>
       <c r="O98">
-        <v>-0.04302361599999998</v>
+        <v>-0.04768011200000002</v>
       </c>
       <c r="P98">
-        <v>-0.1720944639999999</v>
+        <v>-0.1907204480000001</v>
       </c>
       <c r="Q98">
-        <v>-0.002094463999999963</v>
+        <v>-0.02072044800000014</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.271667147647103</v>
+        <v>1.680289530196138</v>
       </c>
       <c r="T98">
-        <v>14.68557255292457</v>
+        <v>19.58076340389944</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1807510769184955</v>
+        <v>0.1788876637543873</v>
       </c>
       <c r="W98">
-        <v>0.1202657419083649</v>
+        <v>0.120539290960856</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9037553845924776</v>
+        <v>0.8944383187719365</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1673317981379145</v>
+        <v>0.1683417981379144</v>
       </c>
       <c r="C99">
-        <v>-4.825799970352652</v>
+        <v>-5.039856562082292</v>
       </c>
       <c r="D99">
-        <v>9.158400029647348</v>
+        <v>9.102943437917707</v>
       </c>
       <c r="E99">
-        <v>13.2242</v>
+        <v>13.3828</v>
       </c>
       <c r="F99">
-        <v>15.3842</v>
+        <v>15.5428</v>
       </c>
       <c r="G99">
         <v>1.4</v>
@@ -9536,37 +9536,37 @@
         <v>2.02</v>
       </c>
       <c r="M99">
-        <v>2.25840056</v>
+        <v>2.28168304</v>
       </c>
       <c r="N99">
-        <v>-0.2384005600000001</v>
+        <v>-0.2616830400000003</v>
       </c>
       <c r="O99">
-        <v>-0.04768011200000002</v>
+        <v>-0.05233660800000006</v>
       </c>
       <c r="P99">
-        <v>-0.1907204480000001</v>
+        <v>-0.2093464320000002</v>
       </c>
       <c r="Q99">
-        <v>-0.02072044800000014</v>
+        <v>-0.03934643200000032</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.680289530196138</v>
+        <v>2.497534295294206</v>
       </c>
       <c r="T99">
-        <v>19.58076340389944</v>
+        <v>29.37114510584915</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1788876637543873</v>
+        <v>0.1770622794303629</v>
       </c>
       <c r="W99">
-        <v>0.120539290960856</v>
+        <v>0.1208072573796227</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8944383187719365</v>
+        <v>0.8853113971518146</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1683417981379144</v>
+        <v>0.1693517981379145</v>
       </c>
       <c r="C100">
-        <v>-5.039856562082292</v>
+        <v>-5.253245586756652</v>
       </c>
       <c r="D100">
-        <v>9.102943437917707</v>
+        <v>9.048154413243347</v>
       </c>
       <c r="E100">
-        <v>13.3828</v>
+        <v>13.5414</v>
       </c>
       <c r="F100">
-        <v>15.5428</v>
+        <v>15.7014</v>
       </c>
       <c r="G100">
         <v>1.4</v>
@@ -9618,37 +9618,37 @@
         <v>2.02</v>
       </c>
       <c r="M100">
-        <v>2.28168304</v>
+        <v>2.30496552</v>
       </c>
       <c r="N100">
-        <v>-0.2616830400000003</v>
+        <v>-0.2849655200000001</v>
       </c>
       <c r="O100">
-        <v>-0.05233660800000006</v>
+        <v>-0.05699310400000002</v>
       </c>
       <c r="P100">
-        <v>-0.2093464320000002</v>
+        <v>-0.2279724160000001</v>
       </c>
       <c r="Q100">
-        <v>-0.03934643200000032</v>
+        <v>-0.05797241600000014</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.497534295294206</v>
+        <v>4.949268590588412</v>
       </c>
       <c r="T100">
-        <v>29.37114510584915</v>
+        <v>58.7422902116983</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1770622794303629</v>
+        <v>0.175273771557329</v>
       </c>
       <c r="W100">
-        <v>0.1208072573796227</v>
+        <v>0.1210698103353841</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8853113971518146</v>
+        <v>0.8763688577866449</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1693517981379145</v>
-      </c>
-      <c r="C101">
-        <v>-5.253245586756652</v>
-      </c>
-      <c r="D101">
-        <v>9.048154413243347</v>
-      </c>
-      <c r="E101">
-        <v>13.5414</v>
-      </c>
-      <c r="F101">
-        <v>15.7014</v>
-      </c>
-      <c r="G101">
-        <v>1.4</v>
-      </c>
-      <c r="H101">
-        <v>13.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.19</v>
-      </c>
-      <c r="K101">
-        <v>0.1699999999999999</v>
-      </c>
-      <c r="L101">
-        <v>2.02</v>
-      </c>
-      <c r="M101">
-        <v>2.30496552</v>
-      </c>
-      <c r="N101">
-        <v>-0.2849655200000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.05699310400000002</v>
-      </c>
-      <c r="P101">
-        <v>-0.2279724160000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.05797241600000014</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.949268590588412</v>
-      </c>
-      <c r="T101">
-        <v>58.7422902116983</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.175273771557329</v>
-      </c>
-      <c r="W101">
-        <v>0.1210698103353841</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8763688577866449</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
